--- a/Docs/Stoned Build Change Logs.xlsx
+++ b/Docs/Stoned Build Change Logs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28129"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shield\Documents\Unity\Stonicorn\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FEC1B0D-21BA-4334-B622-F9340CBD5AC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01E90957-FBC4-49A3-A08B-8EC43A58C21B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6405" yWindow="4245" windowWidth="13695" windowHeight="15345" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="26625" yWindow="6525" windowWidth="18585" windowHeight="12600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Builds" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="918" uniqueCount="761">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="926" uniqueCount="765">
   <si>
     <t>Stoned Builds Change Log</t>
   </si>
@@ -2321,6 +2321,18 @@
   </si>
   <si>
     <t>DQ: didn’t get all blue ability upgrades because the pod was collecting the blue clouds instead of merky xD</t>
+  </si>
+  <si>
+    <t>0.573</t>
+  </si>
+  <si>
+    <t>got interrupted and stopped to take notes, was slow</t>
+  </si>
+  <si>
+    <t>0_573</t>
+  </si>
+  <si>
+    <t>fix some menu bugs, skin: top hat</t>
   </si>
 </sst>
 </file>
@@ -2766,7 +2778,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F588"/>
+  <dimension ref="A1:F589"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.42578125" style="2" bestFit="1" customWidth="1"/>
@@ -6941,6 +6953,23 @@
       </c>
       <c r="E588" t="s">
         <v>758</v>
+      </c>
+    </row>
+    <row r="589" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A589" t="s">
+        <v>763</v>
+      </c>
+      <c r="B589" s="2">
+        <v>45615</v>
+      </c>
+      <c r="C589" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D589" s="4" t="s">
+        <v>692</v>
+      </c>
+      <c r="E589" t="s">
+        <v>764</v>
       </c>
     </row>
   </sheetData>
@@ -6963,7 +6992,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{923D1F1C-9339-49C8-9FCA-FF86526676FD}">
-  <dimension ref="A3:G18"/>
+  <dimension ref="A3:G19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -7269,6 +7298,29 @@
       </c>
       <c r="G18" t="s">
         <v>760</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="6">
+        <v>45615</v>
+      </c>
+      <c r="B19" s="10">
+        <v>0.33750000000000002</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>761</v>
+      </c>
+      <c r="D19" s="15" t="s">
+        <v>743</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>724</v>
+      </c>
+      <c r="F19" s="9">
+        <v>2.0013888888888891</v>
+      </c>
+      <c r="G19" t="s">
+        <v>762</v>
       </c>
     </row>
   </sheetData>

--- a/Docs/Stoned Build Change Logs.xlsx
+++ b/Docs/Stoned Build Change Logs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28227"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shield\Documents\Unity\Stonicorn\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01E90957-FBC4-49A3-A08B-8EC43A58C21B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDD1A644-84A5-4C3D-B46E-887207BCAE63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="26625" yWindow="6525" windowWidth="18585" windowHeight="12600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="21870" windowHeight="12600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Builds" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="926" uniqueCount="765">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="933" uniqueCount="769">
   <si>
     <t>Stoned Builds Change Log</t>
   </si>
@@ -2333,6 +2333,18 @@
   </si>
   <si>
     <t>fix some menu bugs, skin: top hat</t>
+  </si>
+  <si>
+    <t>0.574</t>
+  </si>
+  <si>
+    <t>DQ: missing 2 blue upgrades</t>
+  </si>
+  <si>
+    <t>0_574</t>
+  </si>
+  <si>
+    <t>jungle seed pods</t>
   </si>
 </sst>
 </file>
@@ -2778,7 +2790,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F589"/>
+  <dimension ref="A1:F590"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.42578125" style="2" bestFit="1" customWidth="1"/>
@@ -6970,6 +6982,20 @@
       </c>
       <c r="E589" t="s">
         <v>764</v>
+      </c>
+    </row>
+    <row r="590" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A590" t="s">
+        <v>767</v>
+      </c>
+      <c r="B590" s="2">
+        <v>45627</v>
+      </c>
+      <c r="C590" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E590" t="s">
+        <v>768</v>
       </c>
     </row>
   </sheetData>
@@ -6992,7 +7018,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{923D1F1C-9339-49C8-9FCA-FF86526676FD}">
-  <dimension ref="A3:G19"/>
+  <dimension ref="A3:G20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -7321,6 +7347,29 @@
       </c>
       <c r="G19" t="s">
         <v>762</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="6">
+        <v>45627</v>
+      </c>
+      <c r="B20" s="10">
+        <v>0.92847222222222225</v>
+      </c>
+      <c r="C20" s="12" t="s">
+        <v>765</v>
+      </c>
+      <c r="D20" s="15" t="s">
+        <v>743</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>724</v>
+      </c>
+      <c r="F20" s="9">
+        <v>1.8715277777777777</v>
+      </c>
+      <c r="G20" t="s">
+        <v>766</v>
       </c>
     </row>
   </sheetData>

--- a/Docs/Stoned Build Change Logs.xlsx
+++ b/Docs/Stoned Build Change Logs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shield\Documents\Unity\Stonicorn\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDD1A644-84A5-4C3D-B46E-887207BCAE63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05441689-9096-4ED0-B9E4-7402946C308C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="1950" windowWidth="21870" windowHeight="12600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15975" yWindow="4545" windowWidth="22320" windowHeight="12150" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Builds" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="933" uniqueCount="769">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="940" uniqueCount="772">
   <si>
     <t>Stoned Builds Change Log</t>
   </si>
@@ -2345,6 +2345,15 @@
   </si>
   <si>
     <t>jungle seed pods</t>
+  </si>
+  <si>
+    <t>DNF: game crashed while piloting to the moon. Also took a bathroom break in the middle</t>
+  </si>
+  <si>
+    <t>0_575</t>
+  </si>
+  <si>
+    <t>GravityZone honors Rigidbody2D gravityScale, changed crab grab code</t>
   </si>
 </sst>
 </file>
@@ -2790,7 +2799,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F590"/>
+  <dimension ref="A1:F591"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.42578125" style="2" bestFit="1" customWidth="1"/>
@@ -6996,6 +7005,20 @@
       </c>
       <c r="E590" t="s">
         <v>768</v>
+      </c>
+    </row>
+    <row r="591" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A591" t="s">
+        <v>770</v>
+      </c>
+      <c r="B591" s="2">
+        <v>45658</v>
+      </c>
+      <c r="C591" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E591" t="s">
+        <v>771</v>
       </c>
     </row>
   </sheetData>
@@ -7018,7 +7041,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{923D1F1C-9339-49C8-9FCA-FF86526676FD}">
-  <dimension ref="A3:G20"/>
+  <dimension ref="A3:G21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -7370,6 +7393,29 @@
       </c>
       <c r="G20" t="s">
         <v>766</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="6">
+        <v>45658</v>
+      </c>
+      <c r="B21" s="10">
+        <v>0.58125000000000004</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>765</v>
+      </c>
+      <c r="D21" s="15" t="s">
+        <v>743</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>724</v>
+      </c>
+      <c r="F21" s="9">
+        <v>2.0319444444444446</v>
+      </c>
+      <c r="G21" t="s">
+        <v>769</v>
       </c>
     </row>
   </sheetData>

--- a/Docs/Stoned Build Change Logs.xlsx
+++ b/Docs/Stoned Build Change Logs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shield\Documents\Unity\Stonicorn\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05441689-9096-4ED0-B9E4-7402946C308C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12B35B32-C278-4EA9-BB28-222D143CFF1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15975" yWindow="4545" windowWidth="22320" windowHeight="12150" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="18225" yWindow="4155" windowWidth="18585" windowHeight="14340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Builds" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="940" uniqueCount="772">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="947" uniqueCount="776">
   <si>
     <t>Stoned Builds Change Log</t>
   </si>
@@ -2354,6 +2354,18 @@
   </si>
   <si>
     <t>GravityZone honors Rigidbody2D gravityScale, changed crab grab code</t>
+  </si>
+  <si>
+    <t>0_576</t>
+  </si>
+  <si>
+    <t>Fix floating objects, jungle seed pods dangle with physics</t>
+  </si>
+  <si>
+    <t>0.576</t>
+  </si>
+  <si>
+    <t>DQ: piloted pod collected last blue upgrade, 5 vases self-destructed and granted upgrades immediately, game crashed when trying to get to moon</t>
   </si>
 </sst>
 </file>
@@ -2799,7 +2811,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F591"/>
+  <dimension ref="A1:F592"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.42578125" style="2" bestFit="1" customWidth="1"/>
@@ -7019,6 +7031,20 @@
       </c>
       <c r="E591" t="s">
         <v>771</v>
+      </c>
+    </row>
+    <row r="592" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A592" t="s">
+        <v>772</v>
+      </c>
+      <c r="B592" s="2">
+        <v>45659</v>
+      </c>
+      <c r="C592" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E592" t="s">
+        <v>773</v>
       </c>
     </row>
   </sheetData>
@@ -7041,7 +7067,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{923D1F1C-9339-49C8-9FCA-FF86526676FD}">
-  <dimension ref="A3:G21"/>
+  <dimension ref="A3:G22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -7416,6 +7442,29 @@
       </c>
       <c r="G21" t="s">
         <v>769</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="6">
+        <v>45659</v>
+      </c>
+      <c r="B22" s="10">
+        <v>0.23194444444444445</v>
+      </c>
+      <c r="C22" s="12" t="s">
+        <v>774</v>
+      </c>
+      <c r="D22" s="15" t="s">
+        <v>743</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>724</v>
+      </c>
+      <c r="F22" s="9">
+        <v>1.2986111111111112</v>
+      </c>
+      <c r="G22" t="s">
+        <v>775</v>
       </c>
     </row>
   </sheetData>

--- a/Docs/Stoned Build Change Logs.xlsx
+++ b/Docs/Stoned Build Change Logs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shield\Documents\Unity\Stonicorn\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12B35B32-C278-4EA9-BB28-222D143CFF1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{758D575E-9189-4192-AF05-44C2FB813D98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="18225" yWindow="4155" windowWidth="18585" windowHeight="14340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="16455" yWindow="6450" windowWidth="22830" windowHeight="11880" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Builds" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="947" uniqueCount="776">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="954" uniqueCount="780">
   <si>
     <t>Stoned Builds Change Log</t>
   </si>
@@ -2366,6 +2366,18 @@
   </si>
   <si>
     <t>DQ: piloted pod collected last blue upgrade, 5 vases self-destructed and granted upgrades immediately, game crashed when trying to get to moon</t>
+  </si>
+  <si>
+    <t>0_577</t>
+  </si>
+  <si>
+    <t>Fix save bugs, Fix some object-specific time rewind bugs</t>
+  </si>
+  <si>
+    <t>0.577</t>
+  </si>
+  <si>
+    <t>DQ: red vase and swap upgrade fell through to the core, and I couldn’t get their upgrades</t>
   </si>
 </sst>
 </file>
@@ -2811,7 +2823,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F592"/>
+  <dimension ref="A1:F593"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.42578125" style="2" bestFit="1" customWidth="1"/>
@@ -7045,6 +7057,20 @@
       </c>
       <c r="E592" t="s">
         <v>773</v>
+      </c>
+    </row>
+    <row r="593" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A593" t="s">
+        <v>776</v>
+      </c>
+      <c r="B593" s="2">
+        <v>45660</v>
+      </c>
+      <c r="C593" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E593" t="s">
+        <v>777</v>
       </c>
     </row>
   </sheetData>
@@ -7067,7 +7093,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{923D1F1C-9339-49C8-9FCA-FF86526676FD}">
-  <dimension ref="A3:G22"/>
+  <dimension ref="A3:G23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -7465,6 +7491,29 @@
       </c>
       <c r="G22" t="s">
         <v>775</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="6">
+        <v>45660</v>
+      </c>
+      <c r="B23" s="10">
+        <v>0.29652777777777778</v>
+      </c>
+      <c r="C23" s="12" t="s">
+        <v>778</v>
+      </c>
+      <c r="D23" s="15" t="s">
+        <v>743</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>724</v>
+      </c>
+      <c r="F23" s="9">
+        <v>1.3916666666666666</v>
+      </c>
+      <c r="G23" t="s">
+        <v>779</v>
       </c>
     </row>
   </sheetData>

--- a/Docs/Stoned Build Change Logs.xlsx
+++ b/Docs/Stoned Build Change Logs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shield\Documents\Unity\Stonicorn\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{758D575E-9189-4192-AF05-44C2FB813D98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F996B5B-8181-43CE-97C0-97902DE8A21C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16455" yWindow="6450" windowWidth="22830" windowHeight="11880" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="18225" yWindow="4155" windowWidth="18585" windowHeight="14340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Builds" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="954" uniqueCount="780">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="965" uniqueCount="787">
   <si>
     <t>Stoned Builds Change Log</t>
   </si>
@@ -2378,6 +2378,27 @@
   </si>
   <si>
     <t>DQ: red vase and swap upgrade fell through to the core, and I couldn’t get their upgrades</t>
+  </si>
+  <si>
+    <t>Notable Cells</t>
+  </si>
+  <si>
+    <t>A22, A23</t>
+  </si>
+  <si>
+    <t>Change some entries that used nominal date vs timestamp date</t>
+  </si>
+  <si>
+    <t>(Moved them one date forward)</t>
+  </si>
+  <si>
+    <t>0.578</t>
+  </si>
+  <si>
+    <t>0_578</t>
+  </si>
+  <si>
+    <t>Fix bugs, Fix prefab override issues with ability overrides, Change how the sun collides with player, Make skybox have a gradient</t>
   </si>
 </sst>
 </file>
@@ -2823,7 +2844,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F593"/>
+  <dimension ref="A1:F594"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.42578125" style="2" bestFit="1" customWidth="1"/>
@@ -7071,6 +7092,20 @@
       </c>
       <c r="E593" t="s">
         <v>777</v>
+      </c>
+    </row>
+    <row r="594" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A594" t="s">
+        <v>785</v>
+      </c>
+      <c r="B594" s="2">
+        <v>45661</v>
+      </c>
+      <c r="C594" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E594" t="s">
+        <v>786</v>
       </c>
     </row>
   </sheetData>
@@ -7093,7 +7128,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{923D1F1C-9339-49C8-9FCA-FF86526676FD}">
-  <dimension ref="A3:G23"/>
+  <dimension ref="A3:G24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -7472,7 +7507,7 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="6">
-        <v>45659</v>
+        <v>45660</v>
       </c>
       <c r="B22" s="10">
         <v>0.23194444444444445</v>
@@ -7495,7 +7530,7 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
-        <v>45660</v>
+        <v>45661</v>
       </c>
       <c r="B23" s="10">
         <v>0.29652777777777778</v>
@@ -7514,6 +7549,26 @@
       </c>
       <c r="G23" t="s">
         <v>779</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="6">
+        <v>45662</v>
+      </c>
+      <c r="B24" s="10">
+        <v>0.11527777777777778</v>
+      </c>
+      <c r="C24" s="12" t="s">
+        <v>784</v>
+      </c>
+      <c r="D24" s="15" t="s">
+        <v>743</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>724</v>
+      </c>
+      <c r="F24" s="9">
+        <v>1.2958333333333334</v>
       </c>
     </row>
   </sheetData>
@@ -7524,7 +7579,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D0F1EAA-53CF-4128-A2CE-6FBE41431E7A}">
-  <dimension ref="A3:D4"/>
+  <dimension ref="A3:F5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -7532,7 +7587,7 @@
     <col min="3" max="3" width="48.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -7545,8 +7600,11 @@
       <c r="D3" s="1" t="s">
         <v>749</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E3" s="1" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="6">
         <v>45544</v>
       </c>
@@ -7558,6 +7616,23 @@
       </c>
       <c r="D4" t="s">
         <v>750</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="6">
+        <v>45661</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>748</v>
+      </c>
+      <c r="C5" t="s">
+        <v>782</v>
+      </c>
+      <c r="E5" t="s">
+        <v>781</v>
+      </c>
+      <c r="F5" t="s">
+        <v>783</v>
       </c>
     </row>
   </sheetData>

--- a/Docs/Stoned Build Change Logs.xlsx
+++ b/Docs/Stoned Build Change Logs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shield\Documents\Unity\Stonicorn\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F996B5B-8181-43CE-97C0-97902DE8A21C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E22C8E43-8F8B-46EE-AD69-530E76002F2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="18225" yWindow="4155" windowWidth="18585" windowHeight="14340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="29220" yWindow="6375" windowWidth="18585" windowHeight="14340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Builds" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="965" uniqueCount="787">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="971" uniqueCount="790">
   <si>
     <t>Stoned Builds Change Log</t>
   </si>
@@ -2399,6 +2399,15 @@
   </si>
   <si>
     <t>Fix bugs, Fix prefab override issues with ability overrides, Change how the sun collides with player, Make skybox have a gradient</t>
+  </si>
+  <si>
+    <t>0_579</t>
+  </si>
+  <si>
+    <t>Shield improvements, Flashlight improvements, Fix bug: pilot pod stealing blue upgrades, Fix issues with blue clouds and orange spikeballs</t>
+  </si>
+  <si>
+    <t>0.579</t>
   </si>
 </sst>
 </file>
@@ -2844,7 +2853,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F594"/>
+  <dimension ref="A1:F595"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.42578125" style="2" bestFit="1" customWidth="1"/>
@@ -7106,6 +7115,20 @@
       </c>
       <c r="E594" t="s">
         <v>786</v>
+      </c>
+    </row>
+    <row r="595" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A595" t="s">
+        <v>787</v>
+      </c>
+      <c r="B595" s="2">
+        <v>45662</v>
+      </c>
+      <c r="C595" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E595" t="s">
+        <v>788</v>
       </c>
     </row>
   </sheetData>
@@ -7128,7 +7151,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{923D1F1C-9339-49C8-9FCA-FF86526676FD}">
-  <dimension ref="A3:G24"/>
+  <dimension ref="A3:G25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -7569,6 +7592,26 @@
       </c>
       <c r="F24" s="9">
         <v>1.2958333333333334</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="6">
+        <v>45663</v>
+      </c>
+      <c r="B25" s="10">
+        <v>0.12291666666666666</v>
+      </c>
+      <c r="C25" s="12" t="s">
+        <v>789</v>
+      </c>
+      <c r="D25" s="15" t="s">
+        <v>743</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>724</v>
+      </c>
+      <c r="F25" s="9">
+        <v>1.1597222222222223</v>
       </c>
     </row>
   </sheetData>

--- a/Docs/Stoned Build Change Logs.xlsx
+++ b/Docs/Stoned Build Change Logs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shield\Documents\Unity\Stonicorn\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E22C8E43-8F8B-46EE-AD69-530E76002F2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53D70760-4B31-44D6-84F0-DAFD7149CD60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29220" yWindow="6375" windowWidth="18585" windowHeight="14340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="18225" yWindow="4155" windowWidth="18585" windowHeight="14340" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Builds" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="971" uniqueCount="790">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="977" uniqueCount="793">
   <si>
     <t>Stoned Builds Change Log</t>
   </si>
@@ -2408,6 +2408,15 @@
   </si>
   <si>
     <t>0.579</t>
+  </si>
+  <si>
+    <t>0_580</t>
+  </si>
+  <si>
+    <t>Added road signs</t>
+  </si>
+  <si>
+    <t>0.580</t>
   </si>
 </sst>
 </file>
@@ -2853,7 +2862,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F595"/>
+  <dimension ref="A1:F596"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.42578125" style="2" bestFit="1" customWidth="1"/>
@@ -7131,9 +7140,23 @@
         <v>788</v>
       </c>
     </row>
+    <row r="596" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A596" t="s">
+        <v>790</v>
+      </c>
+      <c r="B596" s="2">
+        <v>45663</v>
+      </c>
+      <c r="C596" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E596" t="s">
+        <v>791</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="C1:D4 C6:D1048576 E95 E99 E102">
+  <conditionalFormatting sqref="C1:D4 E95 E99 E102 C6:D1048576">
     <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>"Unplayable"</formula>
     </cfRule>
@@ -7151,7 +7174,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{923D1F1C-9339-49C8-9FCA-FF86526676FD}">
-  <dimension ref="A3:G25"/>
+  <dimension ref="A3:G26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -7612,6 +7635,26 @@
       </c>
       <c r="F25" s="9">
         <v>1.1597222222222223</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="6">
+        <v>45664</v>
+      </c>
+      <c r="B26" s="10">
+        <v>0.12777777777777777</v>
+      </c>
+      <c r="C26" s="12" t="s">
+        <v>792</v>
+      </c>
+      <c r="D26" s="15" t="s">
+        <v>743</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>724</v>
+      </c>
+      <c r="F26" s="9">
+        <v>0.96111111111111114</v>
       </c>
     </row>
   </sheetData>

--- a/Docs/Stoned Build Change Logs.xlsx
+++ b/Docs/Stoned Build Change Logs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shield\Documents\Unity\Stonicorn\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53D70760-4B31-44D6-84F0-DAFD7149CD60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEC35DFC-DCD5-42CD-917C-41931E292988}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="18225" yWindow="4155" windowWidth="18585" windowHeight="14340" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="18585" yWindow="6150" windowWidth="18660" windowHeight="11850" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Builds" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="977" uniqueCount="793">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="983" uniqueCount="796">
   <si>
     <t>Stoned Builds Change Log</t>
   </si>
@@ -2417,6 +2417,15 @@
   </si>
   <si>
     <t>0.580</t>
+  </si>
+  <si>
+    <t>0.581</t>
+  </si>
+  <si>
+    <t>0_581</t>
+  </si>
+  <si>
+    <t>Improved cactus blossoms, powered movers, Electric Beam ability</t>
   </si>
 </sst>
 </file>
@@ -2862,7 +2871,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F596"/>
+  <dimension ref="A1:F597"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.42578125" style="2" bestFit="1" customWidth="1"/>
@@ -7152,6 +7161,20 @@
       </c>
       <c r="E596" t="s">
         <v>791</v>
+      </c>
+    </row>
+    <row r="597" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A597" t="s">
+        <v>794</v>
+      </c>
+      <c r="B597" s="2">
+        <v>45666</v>
+      </c>
+      <c r="C597" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E597" t="s">
+        <v>795</v>
       </c>
     </row>
   </sheetData>
@@ -7174,7 +7197,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{923D1F1C-9339-49C8-9FCA-FF86526676FD}">
-  <dimension ref="A3:G26"/>
+  <dimension ref="A3:G27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -7655,6 +7678,26 @@
       </c>
       <c r="F26" s="9">
         <v>0.96111111111111114</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="6">
+        <v>45667</v>
+      </c>
+      <c r="B27" s="10">
+        <v>0.23055555555555557</v>
+      </c>
+      <c r="C27" s="12" t="s">
+        <v>793</v>
+      </c>
+      <c r="D27" s="15" t="s">
+        <v>743</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>724</v>
+      </c>
+      <c r="F27" s="9">
+        <v>1.0249999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/Docs/Stoned Build Change Logs.xlsx
+++ b/Docs/Stoned Build Change Logs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shield\Documents\Unity\Stonicorn\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEC35DFC-DCD5-42CD-917C-41931E292988}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51CAF03A-78AD-481E-8244-DCFCEFD6060A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="18585" yWindow="6150" windowWidth="18660" windowHeight="11850" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15975" yWindow="3540" windowWidth="18705" windowHeight="13785" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Builds" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="983" uniqueCount="796">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="990" uniqueCount="800">
   <si>
     <t>Stoned Builds Change Log</t>
   </si>
@@ -2426,6 +2426,18 @@
   </si>
   <si>
     <t>Improved cactus blossoms, powered movers, Electric Beam ability</t>
+  </si>
+  <si>
+    <t>0.582</t>
+  </si>
+  <si>
+    <t>DQ: two red vases were missing, but I still got the upgrades</t>
+  </si>
+  <si>
+    <t>0_582</t>
+  </si>
+  <si>
+    <t>Fixed some framerate issues caused by too many PolygonCollider2Ds, Burst'd CloudMovers, Changed MechFactory entrance</t>
   </si>
 </sst>
 </file>
@@ -2871,7 +2883,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F597"/>
+  <dimension ref="A1:F598"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.42578125" style="2" bestFit="1" customWidth="1"/>
@@ -7177,9 +7189,23 @@
         <v>795</v>
       </c>
     </row>
+    <row r="598" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A598" t="s">
+        <v>798</v>
+      </c>
+      <c r="B598" s="2">
+        <v>45667</v>
+      </c>
+      <c r="C598" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E598" t="s">
+        <v>799</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="C1:D4 E95 E99 E102 C6:D1048576">
+  <conditionalFormatting sqref="C1:D4 C6:D1048576 E95 E99 E102">
     <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>"Unplayable"</formula>
     </cfRule>
@@ -7197,7 +7223,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{923D1F1C-9339-49C8-9FCA-FF86526676FD}">
-  <dimension ref="A3:G27"/>
+  <dimension ref="A3:G28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -7698,6 +7724,29 @@
       </c>
       <c r="F27" s="9">
         <v>1.0249999999999999</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="6">
+        <v>45668</v>
+      </c>
+      <c r="B28" s="10">
+        <v>0.2902777777777778</v>
+      </c>
+      <c r="C28" s="12" t="s">
+        <v>796</v>
+      </c>
+      <c r="D28" s="15" t="s">
+        <v>743</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>724</v>
+      </c>
+      <c r="F28" s="9">
+        <v>0.94444444444444442</v>
+      </c>
+      <c r="G28" t="s">
+        <v>797</v>
       </c>
     </row>
   </sheetData>

--- a/Docs/Stoned Build Change Logs.xlsx
+++ b/Docs/Stoned Build Change Logs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shield\Documents\Unity\Stonicorn\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51CAF03A-78AD-481E-8244-DCFCEFD6060A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{781E0E2F-19D9-4361-9B1D-E18BA945590F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15975" yWindow="3540" windowWidth="18705" windowHeight="13785" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15360" yWindow="4275" windowWidth="18480" windowHeight="10425" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Builds" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="990" uniqueCount="800">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="996" uniqueCount="803">
   <si>
     <t>Stoned Builds Change Log</t>
   </si>
@@ -2438,6 +2438,15 @@
   </si>
   <si>
     <t>Fixed some framerate issues caused by too many PolygonCollider2Ds, Burst'd CloudMovers, Changed MechFactory entrance</t>
+  </si>
+  <si>
+    <t>0_583</t>
+  </si>
+  <si>
+    <t>SceneLoaders take up entire planet area, Yellow has dialogue now</t>
+  </si>
+  <si>
+    <t>0.583</t>
   </si>
 </sst>
 </file>
@@ -2883,7 +2892,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F598"/>
+  <dimension ref="A1:F599"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.42578125" style="2" bestFit="1" customWidth="1"/>
@@ -7203,9 +7212,23 @@
         <v>799</v>
       </c>
     </row>
+    <row r="599" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A599" t="s">
+        <v>800</v>
+      </c>
+      <c r="B599" s="2">
+        <v>45668</v>
+      </c>
+      <c r="C599" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E599" t="s">
+        <v>801</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="C1:D4 C6:D1048576 E95 E99 E102">
+  <conditionalFormatting sqref="C1:D4 E95 E99 E102 C6:D1048576">
     <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>"Unplayable"</formula>
     </cfRule>
@@ -7223,7 +7246,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{923D1F1C-9339-49C8-9FCA-FF86526676FD}">
-  <dimension ref="A3:G28"/>
+  <dimension ref="A3:G29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -7747,6 +7770,26 @@
       </c>
       <c r="G28" t="s">
         <v>797</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="6">
+        <v>45669</v>
+      </c>
+      <c r="B29" s="10">
+        <v>0.33263888888888887</v>
+      </c>
+      <c r="C29" s="12" t="s">
+        <v>802</v>
+      </c>
+      <c r="D29" s="15" t="s">
+        <v>743</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>724</v>
+      </c>
+      <c r="F29" s="9">
+        <v>0.91527777777777775</v>
       </c>
     </row>
   </sheetData>

--- a/Docs/Stoned Build Change Logs.xlsx
+++ b/Docs/Stoned Build Change Logs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shield\Documents\Unity\Stonicorn\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{781E0E2F-19D9-4361-9B1D-E18BA945590F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7AEF7B0-0AAE-49E6-B2E0-60EB1A88C196}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15360" yWindow="4275" windowWidth="18480" windowHeight="10425" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="18225" yWindow="4155" windowWidth="18585" windowHeight="14340" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Builds" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="996" uniqueCount="803">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1003" uniqueCount="807">
   <si>
     <t>Stoned Builds Change Log</t>
   </si>
@@ -2447,6 +2447,18 @@
   </si>
   <si>
     <t>0.583</t>
+  </si>
+  <si>
+    <t>0.584</t>
+  </si>
+  <si>
+    <t>0_584</t>
+  </si>
+  <si>
+    <t>NPC interaction: Kaki</t>
+  </si>
+  <si>
+    <t>DQ: couldn’t find last blue upgrade, got 6 bc of a rewind bug, 2 red vases were in core; and it had numerous low framerate issues</t>
   </si>
 </sst>
 </file>
@@ -2892,7 +2904,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F599"/>
+  <dimension ref="A1:F600"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.42578125" style="2" bestFit="1" customWidth="1"/>
@@ -7226,9 +7238,23 @@
         <v>801</v>
       </c>
     </row>
+    <row r="600" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A600" t="s">
+        <v>804</v>
+      </c>
+      <c r="B600" s="2">
+        <v>45669</v>
+      </c>
+      <c r="C600" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E600" t="s">
+        <v>805</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="C1:D4 E95 E99 E102 C6:D1048576">
+  <conditionalFormatting sqref="C1:D4 C6:D1048576 E95 E99 E102">
     <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>"Unplayable"</formula>
     </cfRule>
@@ -7246,7 +7272,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{923D1F1C-9339-49C8-9FCA-FF86526676FD}">
-  <dimension ref="A3:G29"/>
+  <dimension ref="A3:G30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -7790,6 +7816,29 @@
       </c>
       <c r="F29" s="9">
         <v>0.91527777777777775</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="6">
+        <v>45670</v>
+      </c>
+      <c r="B30" s="10">
+        <v>0.21249999999999999</v>
+      </c>
+      <c r="C30" s="12" t="s">
+        <v>803</v>
+      </c>
+      <c r="D30" s="15" t="s">
+        <v>743</v>
+      </c>
+      <c r="E30" s="7" t="s">
+        <v>724</v>
+      </c>
+      <c r="F30" s="9">
+        <v>1.7034722222222223</v>
+      </c>
+      <c r="G30" t="s">
+        <v>806</v>
       </c>
     </row>
   </sheetData>

--- a/Docs/Stoned Build Change Logs.xlsx
+++ b/Docs/Stoned Build Change Logs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shield\Documents\Unity\Stonicorn\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7AEF7B0-0AAE-49E6-B2E0-60EB1A88C196}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A029413C-C58E-4DFB-AFF9-8909961A7C88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="18225" yWindow="4155" windowWidth="18585" windowHeight="14340" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15360" yWindow="4275" windowWidth="18480" windowHeight="10425" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Builds" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1003" uniqueCount="807">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1010" uniqueCount="811">
   <si>
     <t>Stoned Builds Change Log</t>
   </si>
@@ -2459,6 +2459,18 @@
   </si>
   <si>
     <t>DQ: couldn’t find last blue upgrade, got 6 bc of a rewind bug, 2 red vases were in core; and it had numerous low framerate issues</t>
+  </si>
+  <si>
+    <t>0.585</t>
+  </si>
+  <si>
+    <t>DNF: crashed in well area after 5 swap upgrades, memory objects were saved but rewindables were not fully saved</t>
+  </si>
+  <si>
+    <t>0_585</t>
+  </si>
+  <si>
+    <t>Reduce level load range, Add menu option: NPC dialogue speed and wait time, Add purple eye in menu</t>
   </si>
 </sst>
 </file>
@@ -2904,7 +2916,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F600"/>
+  <dimension ref="A1:F601"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.42578125" style="2" bestFit="1" customWidth="1"/>
@@ -7250,6 +7262,20 @@
       </c>
       <c r="E600" t="s">
         <v>805</v>
+      </c>
+    </row>
+    <row r="601" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A601" t="s">
+        <v>809</v>
+      </c>
+      <c r="B601" s="2">
+        <v>45670</v>
+      </c>
+      <c r="C601" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E601" t="s">
+        <v>810</v>
       </c>
     </row>
   </sheetData>
@@ -7272,7 +7298,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{923D1F1C-9339-49C8-9FCA-FF86526676FD}">
-  <dimension ref="A3:G30"/>
+  <dimension ref="A3:G31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -7839,6 +7865,29 @@
       </c>
       <c r="G30" t="s">
         <v>806</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" s="6">
+        <v>45671</v>
+      </c>
+      <c r="B31" s="10">
+        <v>0.19791666666666666</v>
+      </c>
+      <c r="C31" s="12" t="s">
+        <v>807</v>
+      </c>
+      <c r="D31" s="15" t="s">
+        <v>743</v>
+      </c>
+      <c r="E31" s="7" t="s">
+        <v>724</v>
+      </c>
+      <c r="F31" s="9">
+        <v>0.87847222222222221</v>
+      </c>
+      <c r="G31" t="s">
+        <v>808</v>
       </c>
     </row>
   </sheetData>

--- a/Docs/Stoned Build Change Logs.xlsx
+++ b/Docs/Stoned Build Change Logs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shield\Documents\Unity\Stonicorn\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A029413C-C58E-4DFB-AFF9-8909961A7C88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEADF86D-69C3-4796-89E6-EE91D0D45043}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="15360" yWindow="4275" windowWidth="18480" windowHeight="10425" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1010" uniqueCount="811">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1017" uniqueCount="815">
   <si>
     <t>Stoned Builds Change Log</t>
   </si>
@@ -2471,6 +2471,18 @@
   </si>
   <si>
     <t>Reduce level load range, Add menu option: NPC dialogue speed and wait time, Add purple eye in menu</t>
+  </si>
+  <si>
+    <t>0_586</t>
+  </si>
+  <si>
+    <t>0.586</t>
+  </si>
+  <si>
+    <t>DNF: crashed in well area after 6 swap upgrades, double-tapped first red vase for 2 force launch upgrades</t>
+  </si>
+  <si>
+    <t>NPC base dialogue: Silt the Pebblecorn</t>
   </si>
 </sst>
 </file>
@@ -2916,7 +2928,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F601"/>
+  <dimension ref="A1:F602"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.42578125" style="2" bestFit="1" customWidth="1"/>
@@ -7276,6 +7288,20 @@
       </c>
       <c r="E601" t="s">
         <v>810</v>
+      </c>
+    </row>
+    <row r="602" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A602" t="s">
+        <v>811</v>
+      </c>
+      <c r="B602" s="2">
+        <v>45671</v>
+      </c>
+      <c r="C602" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E602" t="s">
+        <v>814</v>
       </c>
     </row>
   </sheetData>
@@ -7298,7 +7324,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{923D1F1C-9339-49C8-9FCA-FF86526676FD}">
-  <dimension ref="A3:G31"/>
+  <dimension ref="A3:G32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -7888,6 +7914,29 @@
       </c>
       <c r="G31" t="s">
         <v>808</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" s="6">
+        <v>45672</v>
+      </c>
+      <c r="B32" s="10">
+        <v>0.16319444444444445</v>
+      </c>
+      <c r="C32" s="12" t="s">
+        <v>812</v>
+      </c>
+      <c r="D32" s="15" t="s">
+        <v>743</v>
+      </c>
+      <c r="E32" s="7" t="s">
+        <v>724</v>
+      </c>
+      <c r="F32" s="9">
+        <v>0.8208333333333333</v>
+      </c>
+      <c r="G32" t="s">
+        <v>813</v>
       </c>
     </row>
   </sheetData>

--- a/Docs/Stoned Build Change Logs.xlsx
+++ b/Docs/Stoned Build Change Logs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shield\Documents\Unity\Stonicorn\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEADF86D-69C3-4796-89E6-EE91D0D45043}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{387098AE-43E6-4DAC-8B15-C50B34D13582}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15360" yWindow="4275" windowWidth="18480" windowHeight="10425" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="17985" yWindow="5550" windowWidth="19395" windowHeight="10200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Builds" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1017" uniqueCount="815">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="819">
   <si>
     <t>Stoned Builds Change Log</t>
   </si>
@@ -2483,6 +2483,18 @@
   </si>
   <si>
     <t>NPC base dialogue: Silt the Pebblecorn</t>
+  </si>
+  <si>
+    <t>0_587</t>
+  </si>
+  <si>
+    <t>NPC base dialogue: Transistor</t>
+  </si>
+  <si>
+    <t>0.587</t>
+  </si>
+  <si>
+    <t>DNF: crashed in tree on rewinding after collecting 6th wall climb upgrade</t>
   </si>
 </sst>
 </file>
@@ -2928,7 +2940,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F602"/>
+  <dimension ref="A1:F603"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.42578125" style="2" bestFit="1" customWidth="1"/>
@@ -7302,6 +7314,20 @@
       </c>
       <c r="E602" t="s">
         <v>814</v>
+      </c>
+    </row>
+    <row r="603" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A603" t="s">
+        <v>815</v>
+      </c>
+      <c r="B603" s="2">
+        <v>45672</v>
+      </c>
+      <c r="C603" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E603" t="s">
+        <v>816</v>
       </c>
     </row>
   </sheetData>
@@ -7324,7 +7350,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{923D1F1C-9339-49C8-9FCA-FF86526676FD}">
-  <dimension ref="A3:G32"/>
+  <dimension ref="A3:G33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -7937,6 +7963,29 @@
       </c>
       <c r="G32" t="s">
         <v>813</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" s="6">
+        <v>45673</v>
+      </c>
+      <c r="B33" s="10">
+        <v>0.14652777777777778</v>
+      </c>
+      <c r="C33" s="12" t="s">
+        <v>817</v>
+      </c>
+      <c r="D33" s="15" t="s">
+        <v>743</v>
+      </c>
+      <c r="E33" s="7" t="s">
+        <v>724</v>
+      </c>
+      <c r="F33" s="9">
+        <v>0.67361111111111116</v>
+      </c>
+      <c r="G33" t="s">
+        <v>818</v>
       </c>
     </row>
   </sheetData>

--- a/Docs/Stoned Build Change Logs.xlsx
+++ b/Docs/Stoned Build Change Logs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shield\Documents\Unity\Stonicorn\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{387098AE-43E6-4DAC-8B15-C50B34D13582}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82CF760A-D0CD-4E97-9254-9C7659A7291E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17985" yWindow="5550" windowWidth="19395" windowHeight="10200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20835" yWindow="3465" windowWidth="18585" windowHeight="14340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Builds" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="819">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1031" uniqueCount="823">
   <si>
     <t>Stoned Builds Change Log</t>
   </si>
@@ -2495,6 +2495,18 @@
   </si>
   <si>
     <t>DNF: crashed in tree on rewinding after collecting 6th wall climb upgrade</t>
+  </si>
+  <si>
+    <t>0.588</t>
+  </si>
+  <si>
+    <t>DNF: crashed while rewinding after 5 electric upgrades (wall climb only level 1)</t>
+  </si>
+  <si>
+    <t>0_588</t>
+  </si>
+  <si>
+    <t>Adjust sticky pads, Fix bugs, Red vases now contain ability granter, but is not same prefab</t>
   </si>
 </sst>
 </file>
@@ -2940,7 +2952,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F603"/>
+  <dimension ref="A1:F604"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.42578125" style="2" bestFit="1" customWidth="1"/>
@@ -7328,6 +7340,20 @@
       </c>
       <c r="E603" t="s">
         <v>816</v>
+      </c>
+    </row>
+    <row r="604" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A604" t="s">
+        <v>821</v>
+      </c>
+      <c r="B604" s="2">
+        <v>45673</v>
+      </c>
+      <c r="C604" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E604" t="s">
+        <v>822</v>
       </c>
     </row>
   </sheetData>
@@ -7350,7 +7376,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{923D1F1C-9339-49C8-9FCA-FF86526676FD}">
-  <dimension ref="A3:G33"/>
+  <dimension ref="A3:G34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -7986,6 +8012,29 @@
       </c>
       <c r="G33" t="s">
         <v>818</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" s="6">
+        <v>45674</v>
+      </c>
+      <c r="B34" s="10">
+        <v>0.16805555555555557</v>
+      </c>
+      <c r="C34" s="12" t="s">
+        <v>819</v>
+      </c>
+      <c r="D34" s="15" t="s">
+        <v>743</v>
+      </c>
+      <c r="E34" s="7" t="s">
+        <v>724</v>
+      </c>
+      <c r="F34" s="9">
+        <v>0.69791666666666663</v>
+      </c>
+      <c r="G34" t="s">
+        <v>820</v>
       </c>
     </row>
   </sheetData>

--- a/Docs/Stoned Build Change Logs.xlsx
+++ b/Docs/Stoned Build Change Logs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shield\Documents\Unity\Stonicorn\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82CF760A-D0CD-4E97-9254-9C7659A7291E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF8B774D-CE82-4284-92FC-1BC36969AC28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20835" yWindow="3465" windowWidth="18585" windowHeight="14340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1031" uniqueCount="823">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1038" uniqueCount="827">
   <si>
     <t>Stoned Builds Change Log</t>
   </si>
@@ -2507,6 +2507,18 @@
   </si>
   <si>
     <t>Adjust sticky pads, Fix bugs, Red vases now contain ability granter, but is not same prefab</t>
+  </si>
+  <si>
+    <t>0_589</t>
+  </si>
+  <si>
+    <t>Reworked Electric Beam ability, add elevators, NPC base dialogue: Nimbus</t>
+  </si>
+  <si>
+    <t>0.589</t>
+  </si>
+  <si>
+    <t>DQ: all the clouds disappeared so I couldn't get any blue upgrades, some lag and levels loading in and out rapidly (seizure warning!)</t>
   </si>
 </sst>
 </file>
@@ -2952,7 +2964,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F604"/>
+  <dimension ref="A1:F605"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.42578125" style="2" bestFit="1" customWidth="1"/>
@@ -7354,6 +7366,20 @@
       </c>
       <c r="E604" t="s">
         <v>822</v>
+      </c>
+    </row>
+    <row r="605" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A605" t="s">
+        <v>823</v>
+      </c>
+      <c r="B605" s="2">
+        <v>45674</v>
+      </c>
+      <c r="C605" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E605" t="s">
+        <v>824</v>
       </c>
     </row>
   </sheetData>
@@ -7376,7 +7402,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{923D1F1C-9339-49C8-9FCA-FF86526676FD}">
-  <dimension ref="A3:G34"/>
+  <dimension ref="A3:G35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -8035,6 +8061,29 @@
       </c>
       <c r="G34" t="s">
         <v>820</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" s="6">
+        <v>45675</v>
+      </c>
+      <c r="B35" s="10">
+        <v>0.15138888888888888</v>
+      </c>
+      <c r="C35" s="12" t="s">
+        <v>825</v>
+      </c>
+      <c r="D35" s="15" t="s">
+        <v>743</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>724</v>
+      </c>
+      <c r="F35" s="9">
+        <v>1.3194444444444444</v>
+      </c>
+      <c r="G35" t="s">
+        <v>826</v>
       </c>
     </row>
   </sheetData>

--- a/Docs/Stoned Build Change Logs.xlsx
+++ b/Docs/Stoned Build Change Logs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shield\Documents\Unity\Stonicorn\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF8B774D-CE82-4284-92FC-1BC36969AC28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79AF9207-5B59-4E5A-AA5E-EE25AAA848C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20835" yWindow="3465" windowWidth="18585" windowHeight="14340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="21585" yWindow="5625" windowWidth="18480" windowHeight="10425" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Builds" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1038" uniqueCount="827">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1048" uniqueCount="834">
   <si>
     <t>Stoned Builds Change Log</t>
   </si>
@@ -2519,6 +2519,27 @@
   </si>
   <si>
     <t>DQ: all the clouds disappeared so I couldn't get any blue upgrades, some lag and levels loading in and out rapidly (seizure warning!)</t>
+  </si>
+  <si>
+    <t>0_590</t>
+  </si>
+  <si>
+    <t>#613</t>
+  </si>
+  <si>
+    <t>~03:06</t>
+  </si>
+  <si>
+    <t>0.590</t>
+  </si>
+  <si>
+    <t>DNF: work called me in the middle :/</t>
+  </si>
+  <si>
+    <t>#612</t>
+  </si>
+  <si>
+    <t>R18: added an issue that was fixed in this build</t>
   </si>
 </sst>
 </file>
@@ -2964,7 +2985,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F605"/>
+  <dimension ref="A1:F606"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.42578125" style="2" bestFit="1" customWidth="1"/>
@@ -7200,7 +7221,7 @@
         <v>773</v>
       </c>
     </row>
-    <row r="593" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A593" t="s">
         <v>776</v>
       </c>
@@ -7214,7 +7235,7 @@
         <v>777</v>
       </c>
     </row>
-    <row r="594" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A594" t="s">
         <v>785</v>
       </c>
@@ -7228,7 +7249,7 @@
         <v>786</v>
       </c>
     </row>
-    <row r="595" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A595" t="s">
         <v>787</v>
       </c>
@@ -7242,7 +7263,7 @@
         <v>788</v>
       </c>
     </row>
-    <row r="596" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A596" t="s">
         <v>790</v>
       </c>
@@ -7256,7 +7277,7 @@
         <v>791</v>
       </c>
     </row>
-    <row r="597" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A597" t="s">
         <v>794</v>
       </c>
@@ -7270,7 +7291,7 @@
         <v>795</v>
       </c>
     </row>
-    <row r="598" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A598" t="s">
         <v>798</v>
       </c>
@@ -7284,7 +7305,7 @@
         <v>799</v>
       </c>
     </row>
-    <row r="599" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A599" t="s">
         <v>800</v>
       </c>
@@ -7298,7 +7319,7 @@
         <v>801</v>
       </c>
     </row>
-    <row r="600" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A600" t="s">
         <v>804</v>
       </c>
@@ -7312,7 +7333,7 @@
         <v>805</v>
       </c>
     </row>
-    <row r="601" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A601" t="s">
         <v>809</v>
       </c>
@@ -7326,7 +7347,7 @@
         <v>810</v>
       </c>
     </row>
-    <row r="602" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A602" t="s">
         <v>811</v>
       </c>
@@ -7340,7 +7361,7 @@
         <v>814</v>
       </c>
     </row>
-    <row r="603" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A603" t="s">
         <v>815</v>
       </c>
@@ -7354,7 +7375,7 @@
         <v>816</v>
       </c>
     </row>
-    <row r="604" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A604" t="s">
         <v>821</v>
       </c>
@@ -7368,7 +7389,7 @@
         <v>822</v>
       </c>
     </row>
-    <row r="605" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A605" t="s">
         <v>823</v>
       </c>
@@ -7378,13 +7399,33 @@
       <c r="C605" s="2" t="s">
         <v>59</v>
       </c>
+      <c r="D605" s="4" t="s">
+        <v>832</v>
+      </c>
       <c r="E605" t="s">
         <v>824</v>
       </c>
+      <c r="F605" t="s">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="606" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A606" t="s">
+        <v>827</v>
+      </c>
+      <c r="B606" s="2">
+        <v>45675</v>
+      </c>
+      <c r="C606" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D606" s="4" t="s">
+        <v>828</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="C1:D4 C6:D1048576 E95 E99 E102">
+  <conditionalFormatting sqref="C1:D4 E95 E99 E102 C6:D1048576">
     <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>"Unplayable"</formula>
     </cfRule>
@@ -7402,7 +7443,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{923D1F1C-9339-49C8-9FCA-FF86526676FD}">
-  <dimension ref="A3:G35"/>
+  <dimension ref="A3:G36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -8084,6 +8125,29 @@
       </c>
       <c r="G35" t="s">
         <v>826</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" s="6">
+        <v>45676</v>
+      </c>
+      <c r="B36" s="10" t="s">
+        <v>829</v>
+      </c>
+      <c r="C36" s="12" t="s">
+        <v>830</v>
+      </c>
+      <c r="D36" s="15" t="s">
+        <v>743</v>
+      </c>
+      <c r="E36" s="7" t="s">
+        <v>724</v>
+      </c>
+      <c r="F36" s="9">
+        <v>0.60833333333333328</v>
+      </c>
+      <c r="G36" t="s">
+        <v>831</v>
       </c>
     </row>
   </sheetData>

--- a/Docs/Stoned Build Change Logs.xlsx
+++ b/Docs/Stoned Build Change Logs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shield\Documents\Unity\Stonicorn\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79AF9207-5B59-4E5A-AA5E-EE25AAA848C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10ED651C-19CB-484D-B236-D137377B8B7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="21585" yWindow="5625" windowWidth="18480" windowHeight="10425" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10500" yWindow="4020" windowWidth="18930" windowHeight="12870" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Builds" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1048" uniqueCount="834">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1056" uniqueCount="839">
   <si>
     <t>Stoned Builds Change Log</t>
   </si>
@@ -2540,6 +2540,21 @@
   </si>
   <si>
     <t>R18: added an issue that was fixed in this build</t>
+  </si>
+  <si>
+    <t>0.591</t>
+  </si>
+  <si>
+    <t>DNF: crash when launching to the moon, 2 red orbs gave me trouble, I recovered one after a rewind but the other one I didn’t get</t>
+  </si>
+  <si>
+    <t>Skin: Diogenes (Getting Over It)</t>
+  </si>
+  <si>
+    <t>0_591</t>
+  </si>
+  <si>
+    <t>#614, #542</t>
   </si>
 </sst>
 </file>
@@ -2985,7 +3000,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F606"/>
+  <dimension ref="A1:F607"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.42578125" style="2" bestFit="1" customWidth="1"/>
@@ -7423,9 +7438,26 @@
         <v>828</v>
       </c>
     </row>
+    <row r="607" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A607" t="s">
+        <v>837</v>
+      </c>
+      <c r="B607" s="2">
+        <v>45676</v>
+      </c>
+      <c r="C607" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D607" s="4" t="s">
+        <v>838</v>
+      </c>
+      <c r="E607" t="s">
+        <v>836</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="C1:D4 E95 E99 E102 C6:D1048576">
+  <conditionalFormatting sqref="C1:D4 C6:D1048576 E95 E99 E102">
     <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>"Unplayable"</formula>
     </cfRule>
@@ -7443,7 +7475,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{923D1F1C-9339-49C8-9FCA-FF86526676FD}">
-  <dimension ref="A3:G36"/>
+  <dimension ref="A3:G37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -8148,6 +8180,29 @@
       </c>
       <c r="G36" t="s">
         <v>831</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" s="6">
+        <v>45677</v>
+      </c>
+      <c r="B37" s="10">
+        <v>0.27430555555555558</v>
+      </c>
+      <c r="C37" s="12" t="s">
+        <v>834</v>
+      </c>
+      <c r="D37" s="15" t="s">
+        <v>743</v>
+      </c>
+      <c r="E37" s="7" t="s">
+        <v>724</v>
+      </c>
+      <c r="F37" s="9">
+        <v>1.0979166666666667</v>
+      </c>
+      <c r="G37" t="s">
+        <v>835</v>
       </c>
     </row>
   </sheetData>

--- a/Docs/Stoned Build Change Logs.xlsx
+++ b/Docs/Stoned Build Change Logs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shield\Documents\Unity\Stonicorn\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10ED651C-19CB-484D-B236-D137377B8B7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42AFAFAB-BD88-414D-A6C1-DB6A01763820}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10500" yWindow="4020" windowWidth="18930" windowHeight="12870" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10995" yWindow="5310" windowWidth="18720" windowHeight="12330" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Builds" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1056" uniqueCount="839">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1064" uniqueCount="844">
   <si>
     <t>Stoned Builds Change Log</t>
   </si>
@@ -2555,6 +2555,21 @@
   </si>
   <si>
     <t>#614, #542</t>
+  </si>
+  <si>
+    <t>0.592</t>
+  </si>
+  <si>
+    <t>DNF: crash when teleporting from well to end of jungle checkpoint, 1 red orb wasn’t there when I got there</t>
+  </si>
+  <si>
+    <t>0_592</t>
+  </si>
+  <si>
+    <t>#419, #615</t>
+  </si>
+  <si>
+    <t>Fix bugs, Make ObjectState saving more efficient, Past Merkys don’t show up all at once, Setting: Time Rewind Speed</t>
   </si>
 </sst>
 </file>
@@ -3000,7 +3015,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F607"/>
+  <dimension ref="A1:F608"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.42578125" style="2" bestFit="1" customWidth="1"/>
@@ -7455,9 +7470,26 @@
         <v>836</v>
       </c>
     </row>
+    <row r="608" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A608" t="s">
+        <v>841</v>
+      </c>
+      <c r="B608" s="2">
+        <v>45677</v>
+      </c>
+      <c r="C608" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D608" s="4" t="s">
+        <v>842</v>
+      </c>
+      <c r="E608" t="s">
+        <v>843</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="C1:D4 C6:D1048576 E95 E99 E102">
+  <conditionalFormatting sqref="C1:D4 E95 E99 E102 C6:D1048576">
     <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>"Unplayable"</formula>
     </cfRule>
@@ -7475,7 +7507,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{923D1F1C-9339-49C8-9FCA-FF86526676FD}">
-  <dimension ref="A3:G37"/>
+  <dimension ref="A3:G38"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -8203,6 +8235,29 @@
       </c>
       <c r="G37" t="s">
         <v>835</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38" s="6">
+        <v>45678</v>
+      </c>
+      <c r="B38" s="10">
+        <v>8.8888888888888892E-2</v>
+      </c>
+      <c r="C38" s="12" t="s">
+        <v>839</v>
+      </c>
+      <c r="D38" s="15" t="s">
+        <v>743</v>
+      </c>
+      <c r="E38" s="7" t="s">
+        <v>724</v>
+      </c>
+      <c r="F38" s="9">
+        <v>0.88472222222222219</v>
+      </c>
+      <c r="G38" t="s">
+        <v>840</v>
       </c>
     </row>
   </sheetData>

--- a/Docs/Stoned Build Change Logs.xlsx
+++ b/Docs/Stoned Build Change Logs.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
-  <workbookPr/>
+  <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shield\Documents\Unity\Stonicorn\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42AFAFAB-BD88-414D-A6C1-DB6A01763820}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8841EB7D-9ACF-4A54-A8D6-67EF5C547036}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10995" yWindow="5310" windowWidth="18720" windowHeight="12330" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10485" yWindow="5145" windowWidth="18930" windowHeight="12870" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Builds" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1064" uniqueCount="844">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1072" uniqueCount="849">
   <si>
     <t>Stoned Builds Change Log</t>
   </si>
@@ -2570,6 +2570,21 @@
   </si>
   <si>
     <t>Fix bugs, Make ObjectState saving more efficient, Past Merkys don’t show up all at once, Setting: Time Rewind Speed</t>
+  </si>
+  <si>
+    <t>0.593</t>
+  </si>
+  <si>
+    <t>Finished, but I paused the game right after getting in the moon core, then unpaused, and it crashed</t>
+  </si>
+  <si>
+    <t>0_593</t>
+  </si>
+  <si>
+    <t>#617, #618, #619</t>
+  </si>
+  <si>
+    <t>Town: enterable windmill, visitor's center</t>
   </si>
 </sst>
 </file>
@@ -3015,7 +3030,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F608"/>
+  <sheetPr codeName="Sheet1"/>
+  <dimension ref="A1:F609"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.42578125" style="2" bestFit="1" customWidth="1"/>
@@ -7485,6 +7501,23 @@
       </c>
       <c r="E608" t="s">
         <v>843</v>
+      </c>
+    </row>
+    <row r="609" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A609" t="s">
+        <v>846</v>
+      </c>
+      <c r="B609" s="2">
+        <v>45678</v>
+      </c>
+      <c r="C609" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D609" s="4" t="s">
+        <v>847</v>
+      </c>
+      <c r="E609" t="s">
+        <v>848</v>
       </c>
     </row>
   </sheetData>
@@ -7507,7 +7540,8 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{923D1F1C-9339-49C8-9FCA-FF86526676FD}">
-  <dimension ref="A3:G38"/>
+  <sheetPr codeName="Sheet2"/>
+  <dimension ref="A3:G39"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -8260,6 +8294,29 @@
         <v>840</v>
       </c>
     </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" s="6">
+        <v>45679</v>
+      </c>
+      <c r="B39" s="10">
+        <v>0.13333333333333333</v>
+      </c>
+      <c r="C39" s="12" t="s">
+        <v>844</v>
+      </c>
+      <c r="D39" s="15" t="s">
+        <v>743</v>
+      </c>
+      <c r="E39" s="7" t="s">
+        <v>724</v>
+      </c>
+      <c r="F39" s="9">
+        <v>0.99513888888888891</v>
+      </c>
+      <c r="G39" t="s">
+        <v>845</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8268,6 +8325,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D0F1EAA-53CF-4128-A2CE-6FBE41431E7A}">
+  <sheetPr codeName="Sheet3"/>
   <dimension ref="A3:F5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>

--- a/Docs/Stoned Build Change Logs.xlsx
+++ b/Docs/Stoned Build Change Logs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shield\Documents\Unity\Stonicorn\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8841EB7D-9ACF-4A54-A8D6-67EF5C547036}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCD19B47-E607-4572-968C-2245191A7905}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10485" yWindow="5145" windowWidth="18930" windowHeight="12870" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10155" yWindow="5100" windowWidth="18720" windowHeight="12330" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Builds" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1072" uniqueCount="849">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1080" uniqueCount="854">
   <si>
     <t>Stoned Builds Change Log</t>
   </si>
@@ -2585,6 +2585,21 @@
   </si>
   <si>
     <t>Town: enterable windmill, visitor's center</t>
+  </si>
+  <si>
+    <t>0_594</t>
+  </si>
+  <si>
+    <t>#620, #621, #622, #623, #624</t>
+  </si>
+  <si>
+    <t>Stabilize dialogue box sizes, Pilotable Pods now require power, Make GameState a struct</t>
+  </si>
+  <si>
+    <t>0.594</t>
+  </si>
+  <si>
+    <t>DNF: couldn't get red ability, ran into several game-breaking bugs</t>
   </si>
 </sst>
 </file>
@@ -3031,7 +3046,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:F609"/>
+  <dimension ref="A1:F610"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.42578125" style="2" bestFit="1" customWidth="1"/>
@@ -7520,9 +7535,26 @@
         <v>848</v>
       </c>
     </row>
+    <row r="610" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A610" t="s">
+        <v>849</v>
+      </c>
+      <c r="B610" s="2">
+        <v>45679</v>
+      </c>
+      <c r="C610" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D610" s="4" t="s">
+        <v>850</v>
+      </c>
+      <c r="E610" t="s">
+        <v>851</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="C1:D4 E95 E99 E102 C6:D1048576">
+  <conditionalFormatting sqref="C1:D4 C6:D1048576 E95 E99 E102">
     <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>"Unplayable"</formula>
     </cfRule>
@@ -7541,7 +7573,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{923D1F1C-9339-49C8-9FCA-FF86526676FD}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A3:G39"/>
+  <dimension ref="A3:G40"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -8315,6 +8347,29 @@
       </c>
       <c r="G39" t="s">
         <v>845</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" s="6">
+        <v>45680</v>
+      </c>
+      <c r="B40" s="10">
+        <v>0.21527777777777779</v>
+      </c>
+      <c r="C40" s="12" t="s">
+        <v>852</v>
+      </c>
+      <c r="D40" s="15" t="s">
+        <v>743</v>
+      </c>
+      <c r="E40" s="7" t="s">
+        <v>724</v>
+      </c>
+      <c r="F40" s="9">
+        <v>0.70972222222222225</v>
+      </c>
+      <c r="G40" t="s">
+        <v>853</v>
       </c>
     </row>
   </sheetData>

--- a/Docs/Stoned Build Change Logs.xlsx
+++ b/Docs/Stoned Build Change Logs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shield\Documents\Unity\Stonicorn\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCD19B47-E607-4572-968C-2245191A7905}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BB3F40E-7996-47AD-B391-4559E0756156}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10155" yWindow="5100" windowWidth="18720" windowHeight="12330" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5985" yWindow="4170" windowWidth="18585" windowHeight="14340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Builds" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1080" uniqueCount="854">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1087" uniqueCount="858">
   <si>
     <t>Stoned Builds Change Log</t>
   </si>
@@ -2600,6 +2600,18 @@
   </si>
   <si>
     <t>DNF: couldn't get red ability, ran into several game-breaking bugs</t>
+  </si>
+  <si>
+    <t>0.595</t>
+  </si>
+  <si>
+    <t>red orbs / vases gave me two extra upgrades, but no DQ bc I touched all 6 orbs</t>
+  </si>
+  <si>
+    <t>0_595</t>
+  </si>
+  <si>
+    <t>#620, #625, #626</t>
   </si>
 </sst>
 </file>
@@ -3046,7 +3058,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:F610"/>
+  <dimension ref="A1:F611"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.42578125" style="2" bestFit="1" customWidth="1"/>
@@ -7550,6 +7562,20 @@
       </c>
       <c r="E610" t="s">
         <v>851</v>
+      </c>
+    </row>
+    <row r="611" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A611" t="s">
+        <v>856</v>
+      </c>
+      <c r="B611" s="2">
+        <v>45680</v>
+      </c>
+      <c r="C611" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D611" s="4" t="s">
+        <v>857</v>
       </c>
     </row>
   </sheetData>
@@ -7573,7 +7599,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{923D1F1C-9339-49C8-9FCA-FF86526676FD}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A3:G40"/>
+  <dimension ref="A3:G41"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -8370,6 +8396,29 @@
       </c>
       <c r="G40" t="s">
         <v>853</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41" s="6">
+        <v>45681</v>
+      </c>
+      <c r="B41" s="10">
+        <v>0.23125000000000001</v>
+      </c>
+      <c r="C41" s="12" t="s">
+        <v>854</v>
+      </c>
+      <c r="D41" s="15" t="s">
+        <v>743</v>
+      </c>
+      <c r="E41" s="7" t="s">
+        <v>724</v>
+      </c>
+      <c r="F41" s="9">
+        <v>1.3812500000000001</v>
+      </c>
+      <c r="G41" t="s">
+        <v>855</v>
       </c>
     </row>
   </sheetData>

--- a/Docs/Stoned Build Change Logs.xlsx
+++ b/Docs/Stoned Build Change Logs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shield\Documents\Unity\Stonicorn\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BB3F40E-7996-47AD-B391-4559E0756156}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55B1ECB3-1FAE-45A0-96E1-5DAE26D1588C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5985" yWindow="4170" windowWidth="18585" windowHeight="14340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="18225" yWindow="4155" windowWidth="18585" windowHeight="14340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Builds" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1087" uniqueCount="858">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1095" uniqueCount="863">
   <si>
     <t>Stoned Builds Change Log</t>
   </si>
@@ -2612,6 +2612,21 @@
   </si>
   <si>
     <t>#620, #625, #626</t>
+  </si>
+  <si>
+    <t>0.596</t>
+  </si>
+  <si>
+    <t>DNF: lil sis call ^_^</t>
+  </si>
+  <si>
+    <t>0_596</t>
+  </si>
+  <si>
+    <t>#627</t>
+  </si>
+  <si>
+    <t>Improve tutorial visuals</t>
   </si>
 </sst>
 </file>
@@ -3058,7 +3073,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:F611"/>
+  <dimension ref="A1:F612"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.42578125" style="2" bestFit="1" customWidth="1"/>
@@ -7578,9 +7593,26 @@
         <v>857</v>
       </c>
     </row>
+    <row r="612" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A612" t="s">
+        <v>860</v>
+      </c>
+      <c r="B612" s="2">
+        <v>45681</v>
+      </c>
+      <c r="C612" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D612" s="4" t="s">
+        <v>861</v>
+      </c>
+      <c r="E612" t="s">
+        <v>862</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="C1:D4 C6:D1048576 E95 E99 E102">
+  <conditionalFormatting sqref="C1:D4 E95 E99 E102 C6:D1048576">
     <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>"Unplayable"</formula>
     </cfRule>
@@ -7599,7 +7631,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{923D1F1C-9339-49C8-9FCA-FF86526676FD}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A3:G41"/>
+  <dimension ref="A3:G42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -8419,6 +8451,29 @@
       </c>
       <c r="G41" t="s">
         <v>855</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42" s="6">
+        <v>45682</v>
+      </c>
+      <c r="B42" s="10">
+        <v>0.17430555555555555</v>
+      </c>
+      <c r="C42" s="12" t="s">
+        <v>858</v>
+      </c>
+      <c r="D42" s="15" t="s">
+        <v>743</v>
+      </c>
+      <c r="E42" s="7" t="s">
+        <v>724</v>
+      </c>
+      <c r="F42" s="9">
+        <v>0.98750000000000004</v>
+      </c>
+      <c r="G42" t="s">
+        <v>859</v>
       </c>
     </row>
   </sheetData>

--- a/Docs/Stoned Build Change Logs.xlsx
+++ b/Docs/Stoned Build Change Logs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shield\Documents\Unity\Stonicorn\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55B1ECB3-1FAE-45A0-96E1-5DAE26D1588C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC589391-724F-4F0D-B193-8D381E5C5BD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="18225" yWindow="4155" windowWidth="18585" windowHeight="14340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12000" yWindow="6210" windowWidth="18510" windowHeight="12825" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Builds" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1095" uniqueCount="863">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1103" uniqueCount="868">
   <si>
     <t>Stoned Builds Change Log</t>
   </si>
@@ -2627,6 +2627,21 @@
   </si>
   <si>
     <t>Improve tutorial visuals</t>
+  </si>
+  <si>
+    <t>0_597</t>
+  </si>
+  <si>
+    <t>#628</t>
+  </si>
+  <si>
+    <t>Add layers to desert terrain</t>
+  </si>
+  <si>
+    <t>0.597</t>
+  </si>
+  <si>
+    <t>red orb / vase gave me an extra upgrade, but no DQ bc I touched all 6 orbs</t>
   </si>
 </sst>
 </file>
@@ -3073,7 +3088,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:F612"/>
+  <dimension ref="A1:F613"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.42578125" style="2" bestFit="1" customWidth="1"/>
@@ -7608,6 +7623,23 @@
       </c>
       <c r="E612" t="s">
         <v>862</v>
+      </c>
+    </row>
+    <row r="613" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A613" t="s">
+        <v>863</v>
+      </c>
+      <c r="B613" s="2">
+        <v>45682</v>
+      </c>
+      <c r="C613" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D613" s="4" t="s">
+        <v>864</v>
+      </c>
+      <c r="E613" t="s">
+        <v>865</v>
       </c>
     </row>
   </sheetData>
@@ -7631,7 +7663,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{923D1F1C-9339-49C8-9FCA-FF86526676FD}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A3:G42"/>
+  <dimension ref="A3:G43"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -8474,6 +8506,29 @@
       </c>
       <c r="G42" t="s">
         <v>859</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" s="6">
+        <v>45683</v>
+      </c>
+      <c r="B43" s="10">
+        <v>0.22916666666666666</v>
+      </c>
+      <c r="C43" s="12" t="s">
+        <v>866</v>
+      </c>
+      <c r="D43" s="15" t="s">
+        <v>743</v>
+      </c>
+      <c r="E43" s="7" t="s">
+        <v>724</v>
+      </c>
+      <c r="F43" s="9">
+        <v>1.5090277777777779</v>
+      </c>
+      <c r="G43" t="s">
+        <v>867</v>
       </c>
     </row>
   </sheetData>

--- a/Docs/Stoned Build Change Logs.xlsx
+++ b/Docs/Stoned Build Change Logs.xlsx
@@ -8,15 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shield\Documents\Unity\Stonicorn\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC589391-724F-4F0D-B193-8D381E5C5BD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3F58BA6-4AB4-4A7F-8780-2CCEE6EBE0F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12000" yWindow="6210" windowWidth="18510" windowHeight="12825" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9570" yWindow="4275" windowWidth="16755" windowHeight="12645" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Builds" sheetId="1" r:id="rId1"/>
     <sheet name="Speedruns" sheetId="2" r:id="rId2"/>
     <sheet name="Changes" sheetId="3" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Speedruns!$A$3:$G$44</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -38,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1103" uniqueCount="868">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1110" uniqueCount="872">
   <si>
     <t>Stoned Builds Change Log</t>
   </si>
@@ -2642,6 +2645,18 @@
   </si>
   <si>
     <t>red orb / vase gave me an extra upgrade, but no DQ bc I touched all 6 orbs</t>
+  </si>
+  <si>
+    <t>0.598</t>
+  </si>
+  <si>
+    <t>0_598</t>
+  </si>
+  <si>
+    <t>#629</t>
+  </si>
+  <si>
+    <t>Add minecarts to desert</t>
   </si>
 </sst>
 </file>
@@ -3088,7 +3103,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:F613"/>
+  <dimension ref="A1:F614"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.42578125" style="2" bestFit="1" customWidth="1"/>
@@ -7642,9 +7657,26 @@
         <v>865</v>
       </c>
     </row>
+    <row r="614" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A614" t="s">
+        <v>869</v>
+      </c>
+      <c r="B614" s="2">
+        <v>45683</v>
+      </c>
+      <c r="C614" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D614" s="4" t="s">
+        <v>870</v>
+      </c>
+      <c r="E614" t="s">
+        <v>871</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="C1:D4 E95 E99 E102 C6:D1048576">
+  <conditionalFormatting sqref="C1:D4 C6:D1048576 E95 E99 E102">
     <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>"Unplayable"</formula>
     </cfRule>
@@ -7663,7 +7695,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{923D1F1C-9339-49C8-9FCA-FF86526676FD}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A3:G43"/>
+  <dimension ref="A3:G44"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -8531,7 +8563,28 @@
         <v>867</v>
       </c>
     </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" s="6">
+        <v>45684</v>
+      </c>
+      <c r="B44" s="10">
+        <v>0.18124999999999999</v>
+      </c>
+      <c r="C44" s="12" t="s">
+        <v>868</v>
+      </c>
+      <c r="D44" s="15" t="s">
+        <v>743</v>
+      </c>
+      <c r="E44" s="7" t="s">
+        <v>724</v>
+      </c>
+      <c r="F44" s="9">
+        <v>1.3666666666666667</v>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A3:G44" xr:uid="{923D1F1C-9339-49C8-9FCA-FF86526676FD}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Docs/Stoned Build Change Logs.xlsx
+++ b/Docs/Stoned Build Change Logs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shield\Documents\Unity\Stonicorn\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3F58BA6-4AB4-4A7F-8780-2CCEE6EBE0F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEFFAA8D-D2E6-4610-9E3A-238F4CD0EA46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9570" yWindow="4275" windowWidth="16755" windowHeight="12645" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13305" yWindow="3750" windowWidth="16755" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Builds" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1110" uniqueCount="872">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1114" uniqueCount="875">
   <si>
     <t>Stoned Builds Change Log</t>
   </si>
@@ -2657,6 +2657,15 @@
   </si>
   <si>
     <t>Add minecarts to desert</t>
+  </si>
+  <si>
+    <t>0_599</t>
+  </si>
+  <si>
+    <t>#628, #630, #542</t>
+  </si>
+  <si>
+    <t>Hide Diogenes (Getting Over It) better</t>
   </si>
 </sst>
 </file>
@@ -3103,7 +3112,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:F614"/>
+  <dimension ref="A1:F615"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.42578125" style="2" bestFit="1" customWidth="1"/>
@@ -7672,6 +7681,23 @@
       </c>
       <c r="E614" t="s">
         <v>871</v>
+      </c>
+    </row>
+    <row r="615" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A615" t="s">
+        <v>872</v>
+      </c>
+      <c r="B615" s="2">
+        <v>45684</v>
+      </c>
+      <c r="C615" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D615" s="4" t="s">
+        <v>873</v>
+      </c>
+      <c r="E615" t="s">
+        <v>874</v>
       </c>
     </row>
   </sheetData>

--- a/Docs/Stoned Build Change Logs.xlsx
+++ b/Docs/Stoned Build Change Logs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shield\Documents\Unity\Stonicorn\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEFFAA8D-D2E6-4610-9E3A-238F4CD0EA46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63187777-F06C-4313-8C4F-AD8934BA003A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13305" yWindow="3750" windowWidth="16755" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="18225" yWindow="4155" windowWidth="18585" windowHeight="14340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Builds" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1114" uniqueCount="875">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1117" uniqueCount="877">
   <si>
     <t>Stoned Builds Change Log</t>
   </si>
@@ -2666,6 +2666,12 @@
   </si>
   <si>
     <t>Hide Diogenes (Getting Over It) better</t>
+  </si>
+  <si>
+    <t>0_600</t>
+  </si>
+  <si>
+    <t>Expand Jungle area around Well entrance</t>
   </si>
 </sst>
 </file>
@@ -3112,7 +3118,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:F615"/>
+  <dimension ref="A1:F616"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.42578125" style="2" bestFit="1" customWidth="1"/>
@@ -7698,6 +7704,20 @@
       </c>
       <c r="E615" t="s">
         <v>874</v>
+      </c>
+    </row>
+    <row r="616" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A616" t="s">
+        <v>875</v>
+      </c>
+      <c r="B616" s="2">
+        <v>45685</v>
+      </c>
+      <c r="C616" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E616" t="s">
+        <v>876</v>
       </c>
     </row>
   </sheetData>

--- a/Docs/Stoned Build Change Logs.xlsx
+++ b/Docs/Stoned Build Change Logs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shield\Documents\Unity\Stonicorn\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63187777-F06C-4313-8C4F-AD8934BA003A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7BD97A0-6F53-4FC8-B7B4-CECB200F7773}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="18225" yWindow="4155" windowWidth="18585" windowHeight="14340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15765" yWindow="4605" windowWidth="18585" windowHeight="14340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Builds" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1117" uniqueCount="877">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1121" uniqueCount="880">
   <si>
     <t>Stoned Builds Change Log</t>
   </si>
@@ -2672,6 +2672,15 @@
   </si>
   <si>
     <t>Expand Jungle area around Well entrance</t>
+  </si>
+  <si>
+    <t>0_601</t>
+  </si>
+  <si>
+    <t>#631, #617, #629</t>
+  </si>
+  <si>
+    <t>Rework minecart</t>
   </si>
 </sst>
 </file>
@@ -3118,7 +3127,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:F616"/>
+  <dimension ref="A1:F617"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.42578125" style="2" bestFit="1" customWidth="1"/>
@@ -7720,9 +7729,26 @@
         <v>876</v>
       </c>
     </row>
+    <row r="617" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A617" t="s">
+        <v>877</v>
+      </c>
+      <c r="B617" s="2">
+        <v>45686</v>
+      </c>
+      <c r="C617" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D617" s="4" t="s">
+        <v>878</v>
+      </c>
+      <c r="E617" t="s">
+        <v>879</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="C1:D4 C6:D1048576 E95 E99 E102">
+  <conditionalFormatting sqref="C1:D4 E95 E99 E102 C6:D1048576">
     <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>"Unplayable"</formula>
     </cfRule>

--- a/Docs/Stoned Build Change Logs.xlsx
+++ b/Docs/Stoned Build Change Logs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shield\Documents\Unity\Stonicorn\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7BD97A0-6F53-4FC8-B7B4-CECB200F7773}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DE37F11-072F-46F2-BDE8-4948BABC6E36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15765" yWindow="4605" windowWidth="18585" windowHeight="14340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9960" yWindow="6075" windowWidth="15810" windowHeight="13440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Builds" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1121" uniqueCount="880">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1128" uniqueCount="884">
   <si>
     <t>Stoned Builds Change Log</t>
   </si>
@@ -2681,6 +2681,18 @@
   </si>
   <si>
     <t>Rework minecart</t>
+  </si>
+  <si>
+    <t>0.602</t>
+  </si>
+  <si>
+    <t>0_602</t>
+  </si>
+  <si>
+    <t>#375, #628</t>
+  </si>
+  <si>
+    <t>Fix major camera drag issue when dragging near max drag range</t>
   </si>
 </sst>
 </file>
@@ -3127,7 +3139,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:F617"/>
+  <dimension ref="A1:F618"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.42578125" style="2" bestFit="1" customWidth="1"/>
@@ -7744,6 +7756,23 @@
       </c>
       <c r="E617" t="s">
         <v>879</v>
+      </c>
+    </row>
+    <row r="618" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A618" t="s">
+        <v>881</v>
+      </c>
+      <c r="B618" s="2">
+        <v>45687</v>
+      </c>
+      <c r="C618" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D618" s="4" t="s">
+        <v>882</v>
+      </c>
+      <c r="E618" t="s">
+        <v>883</v>
       </c>
     </row>
   </sheetData>
@@ -7767,7 +7796,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{923D1F1C-9339-49C8-9FCA-FF86526676FD}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A3:G44"/>
+  <dimension ref="A3:G45"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -8653,6 +8682,26 @@
       </c>
       <c r="F44" s="9">
         <v>1.3666666666666667</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A45" s="6">
+        <v>45688</v>
+      </c>
+      <c r="B45" s="10">
+        <v>0.27152777777777776</v>
+      </c>
+      <c r="C45" s="12" t="s">
+        <v>880</v>
+      </c>
+      <c r="D45" s="15" t="s">
+        <v>743</v>
+      </c>
+      <c r="E45" s="7" t="s">
+        <v>724</v>
+      </c>
+      <c r="F45" s="9">
+        <v>1.4694444444444446</v>
       </c>
     </row>
   </sheetData>

--- a/Docs/Stoned Build Change Logs.xlsx
+++ b/Docs/Stoned Build Change Logs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shield\Documents\Unity\Stonicorn\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DE37F11-072F-46F2-BDE8-4948BABC6E36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78274A5C-7D93-429F-A995-B46DBCBFAB79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9960" yWindow="6075" windowWidth="15810" windowHeight="13440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19260" yWindow="6450" windowWidth="20475" windowHeight="12570" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Builds" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1128" uniqueCount="884">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1131" uniqueCount="886">
   <si>
     <t>Stoned Builds Change Log</t>
   </si>
@@ -2693,6 +2693,12 @@
   </si>
   <si>
     <t>Fix major camera drag issue when dragging near max drag range</t>
+  </si>
+  <si>
+    <t>0_603</t>
+  </si>
+  <si>
+    <t>#620, #629</t>
   </si>
 </sst>
 </file>
@@ -3139,7 +3145,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:F618"/>
+  <dimension ref="A1:F619"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.42578125" style="2" bestFit="1" customWidth="1"/>
@@ -7775,9 +7781,23 @@
         <v>883</v>
       </c>
     </row>
+    <row r="619" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A619" t="s">
+        <v>884</v>
+      </c>
+      <c r="B619" s="2">
+        <v>45688</v>
+      </c>
+      <c r="C619" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D619" s="4" t="s">
+        <v>885</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="C1:D4 E95 E99 E102 C6:D1048576">
+  <conditionalFormatting sqref="C1:D4 C6:D1048576 E95 E99 E102">
     <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>"Unplayable"</formula>
     </cfRule>

--- a/Docs/Stoned Build Change Logs.xlsx
+++ b/Docs/Stoned Build Change Logs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shield\Documents\Unity\Stonicorn\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78274A5C-7D93-429F-A995-B46DBCBFAB79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{984876D3-3DE0-4808-A292-5C5B5425A006}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19260" yWindow="6450" windowWidth="20475" windowHeight="12570" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="24090" yWindow="6180" windowWidth="17340" windowHeight="13425" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Builds" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1131" uniqueCount="886">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1134" uniqueCount="887">
   <si>
     <t>Stoned Builds Change Log</t>
   </si>
@@ -2699,6 +2699,9 @@
   </si>
   <si>
     <t>#620, #629</t>
+  </si>
+  <si>
+    <t>0.603</t>
   </si>
 </sst>
 </file>
@@ -7816,7 +7819,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{923D1F1C-9339-49C8-9FCA-FF86526676FD}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A3:G45"/>
+  <dimension ref="A3:G46"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -8722,6 +8725,26 @@
       </c>
       <c r="F45" s="9">
         <v>1.4694444444444446</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46" s="6">
+        <v>45692</v>
+      </c>
+      <c r="B46" s="10">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="C46" s="12" t="s">
+        <v>886</v>
+      </c>
+      <c r="D46" s="15" t="s">
+        <v>743</v>
+      </c>
+      <c r="E46" s="7" t="s">
+        <v>724</v>
+      </c>
+      <c r="F46" s="9">
+        <v>1.3805555555555555</v>
       </c>
     </row>
   </sheetData>

--- a/Docs/Stoned Build Change Logs.xlsx
+++ b/Docs/Stoned Build Change Logs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shield\Documents\Unity\Stonicorn\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{984876D3-3DE0-4808-A292-5C5B5425A006}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0624A084-A6B8-48B3-A6AD-5494A26B5551}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="24090" yWindow="6180" windowWidth="17340" windowHeight="13425" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22380" yWindow="6765" windowWidth="15480" windowHeight="11820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Builds" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1134" uniqueCount="887">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1137" uniqueCount="889">
   <si>
     <t>Stoned Builds Change Log</t>
   </si>
@@ -2702,6 +2702,12 @@
   </si>
   <si>
     <t>0.603</t>
+  </si>
+  <si>
+    <t>0_604</t>
+  </si>
+  <si>
+    <t>#632</t>
   </si>
 </sst>
 </file>
@@ -3148,7 +3154,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:F619"/>
+  <dimension ref="A1:F620"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.42578125" style="2" bestFit="1" customWidth="1"/>
@@ -7796,6 +7802,20 @@
       </c>
       <c r="D619" s="4" t="s">
         <v>885</v>
+      </c>
+    </row>
+    <row r="620" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A620" t="s">
+        <v>887</v>
+      </c>
+      <c r="B620" s="2">
+        <v>45694</v>
+      </c>
+      <c r="C620" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D620" s="4" t="s">
+        <v>888</v>
       </c>
     </row>
   </sheetData>

--- a/Docs/Stoned Build Change Logs.xlsx
+++ b/Docs/Stoned Build Change Logs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shield\Documents\Unity\Stonicorn\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0624A084-A6B8-48B3-A6AD-5494A26B5551}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0562A136-2559-40CB-A2E1-2457B3ACD6BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22380" yWindow="6765" windowWidth="15480" windowHeight="11820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="16890" yWindow="5115" windowWidth="15480" windowHeight="11820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Builds" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1137" uniqueCount="889">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1145" uniqueCount="894">
   <si>
     <t>Stoned Builds Change Log</t>
   </si>
@@ -2708,6 +2708,21 @@
   </si>
   <si>
     <t>#632</t>
+  </si>
+  <si>
+    <t>0.605</t>
+  </si>
+  <si>
+    <t>red orb / vases gave me full upgrade early, but no DQ but I touched all 6 orbs</t>
+  </si>
+  <si>
+    <t>0_605</t>
+  </si>
+  <si>
+    <t>#633, #634</t>
+  </si>
+  <si>
+    <t>Make treetops rounder in jungle</t>
   </si>
 </sst>
 </file>
@@ -3154,7 +3169,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:F620"/>
+  <dimension ref="A1:F621"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.42578125" style="2" bestFit="1" customWidth="1"/>
@@ -7818,9 +7833,26 @@
         <v>888</v>
       </c>
     </row>
+    <row r="621" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A621" t="s">
+        <v>891</v>
+      </c>
+      <c r="B621" s="2">
+        <v>45695</v>
+      </c>
+      <c r="C621" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D621" s="4" t="s">
+        <v>892</v>
+      </c>
+      <c r="E621" t="s">
+        <v>893</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="C1:D4 C6:D1048576 E95 E99 E102">
+  <conditionalFormatting sqref="C1:D4 E95 E99 E102 C6:D1048576">
     <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>"Unplayable"</formula>
     </cfRule>
@@ -7839,7 +7871,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{923D1F1C-9339-49C8-9FCA-FF86526676FD}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A3:G46"/>
+  <dimension ref="A3:G47"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -8765,6 +8797,29 @@
       </c>
       <c r="F46" s="9">
         <v>1.3805555555555555</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A47" s="6">
+        <v>45696</v>
+      </c>
+      <c r="B47" s="10">
+        <v>0.27569444444444446</v>
+      </c>
+      <c r="C47" s="12" t="s">
+        <v>889</v>
+      </c>
+      <c r="D47" s="15" t="s">
+        <v>743</v>
+      </c>
+      <c r="E47" s="7" t="s">
+        <v>724</v>
+      </c>
+      <c r="F47" s="9">
+        <v>1.2527777777777778</v>
+      </c>
+      <c r="G47" t="s">
+        <v>890</v>
       </c>
     </row>
   </sheetData>

--- a/Docs/Stoned Build Change Logs.xlsx
+++ b/Docs/Stoned Build Change Logs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shield\Documents\Unity\Stonicorn\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0562A136-2559-40CB-A2E1-2457B3ACD6BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40DCFAE3-A07F-4AD4-BEE2-267FEAB9FBDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16890" yWindow="5115" windowWidth="15480" windowHeight="11820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11460" yWindow="6225" windowWidth="17340" windowHeight="13425" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Builds" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1145" uniqueCount="894">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1153" uniqueCount="899">
   <si>
     <t>Stoned Builds Change Log</t>
   </si>
@@ -2723,6 +2723,21 @@
   </si>
   <si>
     <t>Make treetops rounder in jungle</t>
+  </si>
+  <si>
+    <t>0_606</t>
+  </si>
+  <si>
+    <t>#635, #634</t>
+  </si>
+  <si>
+    <t>Refactor: AutoInitialize tag</t>
+  </si>
+  <si>
+    <t>0.606</t>
+  </si>
+  <si>
+    <t>DNF: game completely unplayable</t>
   </si>
 </sst>
 </file>
@@ -3169,7 +3184,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:F621"/>
+  <dimension ref="A1:F622"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.42578125" style="2" bestFit="1" customWidth="1"/>
@@ -7850,9 +7865,26 @@
         <v>893</v>
       </c>
     </row>
+    <row r="622" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A622" t="s">
+        <v>894</v>
+      </c>
+      <c r="B622" s="2">
+        <v>45696</v>
+      </c>
+      <c r="C622" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D622" s="4" t="s">
+        <v>895</v>
+      </c>
+      <c r="E622" t="s">
+        <v>896</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="C1:D4 E95 E99 E102 C6:D1048576">
+  <conditionalFormatting sqref="C1:D4 C6:D1048576 E95 E99 E102">
     <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>"Unplayable"</formula>
     </cfRule>
@@ -7871,7 +7903,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{923D1F1C-9339-49C8-9FCA-FF86526676FD}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A3:G47"/>
+  <dimension ref="A3:G48"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -8820,6 +8852,29 @@
       </c>
       <c r="G47" t="s">
         <v>890</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A48" s="6">
+        <v>45697</v>
+      </c>
+      <c r="B48" s="10">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="C48" s="12" t="s">
+        <v>897</v>
+      </c>
+      <c r="D48" s="15" t="s">
+        <v>743</v>
+      </c>
+      <c r="E48" s="7" t="s">
+        <v>724</v>
+      </c>
+      <c r="F48" s="9">
+        <v>7.5231481481481482E-4</v>
+      </c>
+      <c r="G48" t="s">
+        <v>898</v>
       </c>
     </row>
   </sheetData>

--- a/Docs/Stoned Build Change Logs.xlsx
+++ b/Docs/Stoned Build Change Logs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shield\Documents\Unity\Stonicorn\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40DCFAE3-A07F-4AD4-BEE2-267FEAB9FBDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7CC9712-B6FD-437A-BDED-FF6320079F4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11460" yWindow="6225" windowWidth="17340" windowHeight="13425" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4680" yWindow="4680" windowWidth="21840" windowHeight="12480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Builds" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1153" uniqueCount="899">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1159" uniqueCount="902">
   <si>
     <t>Stoned Builds Change Log</t>
   </si>
@@ -2738,6 +2738,15 @@
   </si>
   <si>
     <t>DNF: game completely unplayable</t>
+  </si>
+  <si>
+    <t>0.607</t>
+  </si>
+  <si>
+    <t>0_607</t>
+  </si>
+  <si>
+    <t>#634</t>
   </si>
 </sst>
 </file>
@@ -3184,7 +3193,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:F622"/>
+  <dimension ref="A1:F623"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.42578125" style="2" bestFit="1" customWidth="1"/>
@@ -7880,6 +7889,20 @@
       </c>
       <c r="E622" t="s">
         <v>896</v>
+      </c>
+    </row>
+    <row r="623" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A623" t="s">
+        <v>900</v>
+      </c>
+      <c r="B623" s="2">
+        <v>45697</v>
+      </c>
+      <c r="C623" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D623" s="4" t="s">
+        <v>901</v>
       </c>
     </row>
   </sheetData>
@@ -7903,7 +7926,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{923D1F1C-9339-49C8-9FCA-FF86526676FD}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A3:G48"/>
+  <dimension ref="A3:G49"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -8875,6 +8898,26 @@
       </c>
       <c r="G48" t="s">
         <v>898</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" s="6">
+        <v>45698</v>
+      </c>
+      <c r="B49" s="10">
+        <v>0.30833333333333335</v>
+      </c>
+      <c r="C49" s="12" t="s">
+        <v>899</v>
+      </c>
+      <c r="D49" s="15" t="s">
+        <v>743</v>
+      </c>
+      <c r="E49" s="7" t="s">
+        <v>724</v>
+      </c>
+      <c r="F49" s="9">
+        <v>1.2756944444444445</v>
       </c>
     </row>
   </sheetData>

--- a/Docs/Stoned Build Change Logs.xlsx
+++ b/Docs/Stoned Build Change Logs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shield\Documents\Unity\Stonicorn\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7CC9712-B6FD-437A-BDED-FF6320079F4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CA7DCC7-0DFD-43C9-8FF0-CC223BC70DB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4680" yWindow="4680" windowWidth="21840" windowHeight="12480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13590" yWindow="4695" windowWidth="25845" windowHeight="14010" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Builds" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="Changes" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Speedruns!$A$3:$G$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Speedruns!$A$3:$G$50</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1159" uniqueCount="902">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1165" uniqueCount="904">
   <si>
     <t>Stoned Builds Change Log</t>
   </si>
@@ -2747,6 +2747,12 @@
   </si>
   <si>
     <t>#634</t>
+  </si>
+  <si>
+    <t>0.608</t>
+  </si>
+  <si>
+    <t>0_608</t>
   </si>
 </sst>
 </file>
@@ -3193,7 +3199,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:F623"/>
+  <dimension ref="A1:F624"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.42578125" style="2" bestFit="1" customWidth="1"/>
@@ -7905,9 +7911,23 @@
         <v>901</v>
       </c>
     </row>
+    <row r="624" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A624" t="s">
+        <v>903</v>
+      </c>
+      <c r="B624" s="2">
+        <v>45698</v>
+      </c>
+      <c r="C624" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D624" s="4" t="s">
+        <v>901</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="C1:D4 C6:D1048576 E95 E99 E102">
+  <conditionalFormatting sqref="C1:D4 E95 E99 E102 C6:D1048576">
     <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>"Unplayable"</formula>
     </cfRule>
@@ -7926,7 +7946,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{923D1F1C-9339-49C8-9FCA-FF86526676FD}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A3:G49"/>
+  <dimension ref="A3:G50"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -8920,8 +8940,28 @@
         <v>1.2756944444444445</v>
       </c>
     </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="6">
+        <v>45699</v>
+      </c>
+      <c r="B50" s="10">
+        <v>0.25138888888888888</v>
+      </c>
+      <c r="C50" s="12" t="s">
+        <v>902</v>
+      </c>
+      <c r="D50" s="15" t="s">
+        <v>732</v>
+      </c>
+      <c r="E50" s="7" t="s">
+        <v>724</v>
+      </c>
+      <c r="F50" s="9">
+        <v>0.3611111111111111</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:G44" xr:uid="{923D1F1C-9339-49C8-9FCA-FF86526676FD}"/>
+  <autoFilter ref="A3:G50" xr:uid="{923D1F1C-9339-49C8-9FCA-FF86526676FD}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Docs/Stoned Build Change Logs.xlsx
+++ b/Docs/Stoned Build Change Logs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shield\Documents\Unity\Stonicorn\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CA7DCC7-0DFD-43C9-8FF0-CC223BC70DB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67B70771-7FA7-4A1C-90BE-019071B94566}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13590" yWindow="4695" windowWidth="25845" windowHeight="14010" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="21840" windowHeight="12480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Builds" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1165" uniqueCount="904">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1172" uniqueCount="908">
   <si>
     <t>Stoned Builds Change Log</t>
   </si>
@@ -2753,6 +2753,18 @@
   </si>
   <si>
     <t>0_608</t>
+  </si>
+  <si>
+    <t>0.609</t>
+  </si>
+  <si>
+    <t>DNF: kaki wouldn’t recognize that I tried to leave, game broke when trying to rewind just after getting electric ability</t>
+  </si>
+  <si>
+    <t>0_609</t>
+  </si>
+  <si>
+    <t>#634, #637</t>
   </si>
 </sst>
 </file>
@@ -3199,7 +3211,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:F624"/>
+  <dimension ref="A1:F625"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.42578125" style="2" bestFit="1" customWidth="1"/>
@@ -7925,9 +7937,23 @@
         <v>901</v>
       </c>
     </row>
+    <row r="625" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A625" t="s">
+        <v>906</v>
+      </c>
+      <c r="B625" s="2">
+        <v>45699</v>
+      </c>
+      <c r="C625" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D625" s="4" t="s">
+        <v>907</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="C1:D4 E95 E99 E102 C6:D1048576">
+  <conditionalFormatting sqref="C1:D4 C6:D1048576 E95 E99 E102">
     <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>"Unplayable"</formula>
     </cfRule>
@@ -7946,7 +7972,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{923D1F1C-9339-49C8-9FCA-FF86526676FD}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A3:G50"/>
+  <dimension ref="A3:G51"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -8920,7 +8946,7 @@
         <v>898</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="6">
         <v>45698</v>
       </c>
@@ -8940,7 +8966,7 @@
         <v>1.2756944444444445</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="6">
         <v>45699</v>
       </c>
@@ -8958,6 +8984,29 @@
       </c>
       <c r="F50" s="9">
         <v>0.3611111111111111</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A51" s="6">
+        <v>45700</v>
+      </c>
+      <c r="B51" s="10">
+        <v>0.2590277777777778</v>
+      </c>
+      <c r="C51" s="12" t="s">
+        <v>904</v>
+      </c>
+      <c r="D51" s="15" t="s">
+        <v>732</v>
+      </c>
+      <c r="E51" s="7" t="s">
+        <v>724</v>
+      </c>
+      <c r="F51" s="9">
+        <v>0.2590277777777778</v>
+      </c>
+      <c r="G51" t="s">
+        <v>905</v>
       </c>
     </row>
   </sheetData>

--- a/Docs/Stoned Build Change Logs.xlsx
+++ b/Docs/Stoned Build Change Logs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shield\Documents\Unity\Stonicorn\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67B70771-7FA7-4A1C-90BE-019071B94566}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4DDDC6B-3AC7-427C-96C8-2DBC83EE1D00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="21840" windowHeight="12480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="345" yWindow="4230" windowWidth="16005" windowHeight="14685" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Builds" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1172" uniqueCount="908">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1179" uniqueCount="911">
   <si>
     <t>Stoned Builds Change Log</t>
   </si>
@@ -2765,6 +2765,15 @@
   </si>
   <si>
     <t>#634, #637</t>
+  </si>
+  <si>
+    <t>0.610</t>
+  </si>
+  <si>
+    <t>0_610</t>
+  </si>
+  <si>
+    <t>Make reverse basic traversal impossible if you don't know the double teleport trick</t>
   </si>
 </sst>
 </file>
@@ -3211,7 +3220,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:F625"/>
+  <dimension ref="A1:F626"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.42578125" style="2" bestFit="1" customWidth="1"/>
@@ -7937,7 +7946,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="625" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A625" t="s">
         <v>906</v>
       </c>
@@ -7949,6 +7958,23 @@
       </c>
       <c r="D625" s="4" t="s">
         <v>907</v>
+      </c>
+    </row>
+    <row r="626" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A626" t="s">
+        <v>909</v>
+      </c>
+      <c r="B626" s="2">
+        <v>45700</v>
+      </c>
+      <c r="C626" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D626" s="4" t="s">
+        <v>901</v>
+      </c>
+      <c r="E626" t="s">
+        <v>910</v>
       </c>
     </row>
   </sheetData>
@@ -7972,7 +7998,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{923D1F1C-9339-49C8-9FCA-FF86526676FD}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A3:G51"/>
+  <dimension ref="A3:G52"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -9007,6 +9033,26 @@
       </c>
       <c r="G51" t="s">
         <v>905</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A52" s="6">
+        <v>45701</v>
+      </c>
+      <c r="B52" s="10">
+        <v>0.16458333333333333</v>
+      </c>
+      <c r="C52" s="12" t="s">
+        <v>908</v>
+      </c>
+      <c r="D52" s="15" t="s">
+        <v>732</v>
+      </c>
+      <c r="E52" s="7" t="s">
+        <v>724</v>
+      </c>
+      <c r="F52" s="9">
+        <v>0.38680555555555557</v>
       </c>
     </row>
   </sheetData>

--- a/Docs/Stoned Build Change Logs.xlsx
+++ b/Docs/Stoned Build Change Logs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shield\Documents\Unity\Stonicorn\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4DDDC6B-3AC7-427C-96C8-2DBC83EE1D00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E36627FF-6A0C-4385-AE5B-2317618F5B06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="345" yWindow="4230" windowWidth="16005" windowHeight="14685" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="16965" yWindow="3105" windowWidth="22875" windowHeight="15045" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Builds" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1179" uniqueCount="911">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1187" uniqueCount="916">
   <si>
     <t>Stoned Builds Change Log</t>
   </si>
@@ -2774,6 +2774,21 @@
   </si>
   <si>
     <t>Make reverse basic traversal impossible if you don't know the double teleport trick</t>
+  </si>
+  <si>
+    <t>0_611</t>
+  </si>
+  <si>
+    <t>#634, #638</t>
+  </si>
+  <si>
+    <t>Add more "door openers" to mech factory</t>
+  </si>
+  <si>
+    <t>0.611</t>
+  </si>
+  <si>
+    <t>DNF: game broke when rewinding at snail ceiling break puzzle</t>
   </si>
 </sst>
 </file>
@@ -3220,7 +3235,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:F626"/>
+  <dimension ref="A1:F627"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.42578125" style="2" bestFit="1" customWidth="1"/>
@@ -7977,9 +7992,26 @@
         <v>910</v>
       </c>
     </row>
+    <row r="627" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A627" t="s">
+        <v>911</v>
+      </c>
+      <c r="B627" s="2">
+        <v>45701</v>
+      </c>
+      <c r="C627" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D627" s="4" t="s">
+        <v>912</v>
+      </c>
+      <c r="E627" t="s">
+        <v>913</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="C1:D4 C6:D1048576 E95 E99 E102">
+  <conditionalFormatting sqref="C1:D4 E95 E99 E102 C6:D1048576">
     <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>"Unplayable"</formula>
     </cfRule>
@@ -7998,7 +8030,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{923D1F1C-9339-49C8-9FCA-FF86526676FD}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A3:G52"/>
+  <dimension ref="A3:G53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -9053,6 +9085,29 @@
       </c>
       <c r="F52" s="9">
         <v>0.38680555555555557</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A53" s="6">
+        <v>45702</v>
+      </c>
+      <c r="B53" s="10">
+        <v>0.20902777777777778</v>
+      </c>
+      <c r="C53" s="12" t="s">
+        <v>914</v>
+      </c>
+      <c r="D53" s="15" t="s">
+        <v>732</v>
+      </c>
+      <c r="E53" s="7" t="s">
+        <v>724</v>
+      </c>
+      <c r="F53" s="9">
+        <v>8.4722222222222227E-2</v>
+      </c>
+      <c r="G53" t="s">
+        <v>915</v>
       </c>
     </row>
   </sheetData>

--- a/Docs/Stoned Build Change Logs.xlsx
+++ b/Docs/Stoned Build Change Logs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shield\Documents\Unity\Stonicorn\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E36627FF-6A0C-4385-AE5B-2317618F5B06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{789DEFD7-D1EB-408E-AB49-B0B403A6E642}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16965" yWindow="3105" windowWidth="22875" windowHeight="15045" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="345" yWindow="4500" windowWidth="15360" windowHeight="15000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Builds" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1187" uniqueCount="916">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1190" uniqueCount="917">
   <si>
     <t>Stoned Builds Change Log</t>
   </si>
@@ -2789,6 +2789,9 @@
   </si>
   <si>
     <t>DNF: game broke when rewinding at snail ceiling break puzzle</t>
+  </si>
+  <si>
+    <t>0_611b</t>
   </si>
 </sst>
 </file>
@@ -3235,7 +3238,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:F627"/>
+  <dimension ref="A1:F628"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.42578125" style="2" bestFit="1" customWidth="1"/>
@@ -8009,9 +8012,23 @@
         <v>913</v>
       </c>
     </row>
+    <row r="628" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A628" t="s">
+        <v>916</v>
+      </c>
+      <c r="B628" s="2">
+        <v>45702</v>
+      </c>
+      <c r="C628" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D628" s="4" t="s">
+        <v>901</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="C1:D4 E95 E99 E102 C6:D1048576">
+  <conditionalFormatting sqref="C1:D4 C6:D1048576 E95 E99 E102">
     <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>"Unplayable"</formula>
     </cfRule>

--- a/Docs/Stoned Build Change Logs.xlsx
+++ b/Docs/Stoned Build Change Logs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shield\Documents\Unity\Stonicorn\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{789DEFD7-D1EB-408E-AB49-B0B403A6E642}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48C06AC4-15C1-4F28-8BD0-3139B446B9AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="345" yWindow="4500" windowWidth="15360" windowHeight="15000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="16590" yWindow="2250" windowWidth="15660" windowHeight="12075" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Builds" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1190" uniqueCount="917">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1197" uniqueCount="921">
   <si>
     <t>Stoned Builds Change Log</t>
   </si>
@@ -2792,6 +2792,18 @@
   </si>
   <si>
     <t>0_611b</t>
+  </si>
+  <si>
+    <t>0.612</t>
+  </si>
+  <si>
+    <t>Enemy: Snake</t>
+  </si>
+  <si>
+    <t>0_612</t>
+  </si>
+  <si>
+    <t>#634, #640</t>
   </si>
 </sst>
 </file>
@@ -3238,7 +3250,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:F628"/>
+  <dimension ref="A1:F629"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.42578125" style="2" bestFit="1" customWidth="1"/>
@@ -8026,9 +8038,26 @@
         <v>901</v>
       </c>
     </row>
+    <row r="629" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A629" t="s">
+        <v>919</v>
+      </c>
+      <c r="B629" s="2">
+        <v>45702</v>
+      </c>
+      <c r="C629" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D629" s="4" t="s">
+        <v>920</v>
+      </c>
+      <c r="E629" t="s">
+        <v>918</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="C1:D4 C6:D1048576 E95 E99 E102">
+  <conditionalFormatting sqref="C1:D4 E95 E99 E102 C6:D1048576">
     <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>"Unplayable"</formula>
     </cfRule>
@@ -8047,7 +8076,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{923D1F1C-9339-49C8-9FCA-FF86526676FD}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A3:G53"/>
+  <dimension ref="A3:G54"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -9125,6 +9154,26 @@
       </c>
       <c r="G53" t="s">
         <v>915</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A54" s="6">
+        <v>45703</v>
+      </c>
+      <c r="B54" s="10">
+        <v>0.16180555555555556</v>
+      </c>
+      <c r="C54" s="12" t="s">
+        <v>917</v>
+      </c>
+      <c r="D54" s="15" t="s">
+        <v>732</v>
+      </c>
+      <c r="E54" s="7" t="s">
+        <v>724</v>
+      </c>
+      <c r="F54" s="9">
+        <v>0.4548611111111111</v>
       </c>
     </row>
   </sheetData>

--- a/Docs/Stoned Build Change Logs.xlsx
+++ b/Docs/Stoned Build Change Logs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shield\Documents\Unity\Stonicorn\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48C06AC4-15C1-4F28-8BD0-3139B446B9AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7A3091E-529F-41F2-988E-3EE5F5F5FF05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16590" yWindow="2250" windowWidth="15660" windowHeight="12075" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9675" yWindow="5970" windowWidth="16065" windowHeight="12330" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Builds" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1197" uniqueCount="921">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1203" uniqueCount="924">
   <si>
     <t>Stoned Builds Change Log</t>
   </si>
@@ -2804,6 +2804,15 @@
   </si>
   <si>
     <t>#634, #640</t>
+  </si>
+  <si>
+    <t>0.613</t>
+  </si>
+  <si>
+    <t>0_613</t>
+  </si>
+  <si>
+    <t>#641, #642, #634, #640</t>
   </si>
 </sst>
 </file>
@@ -3250,7 +3259,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:F629"/>
+  <dimension ref="A1:F630"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.42578125" style="2" bestFit="1" customWidth="1"/>
@@ -8055,9 +8064,23 @@
         <v>918</v>
       </c>
     </row>
+    <row r="630" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A630" t="s">
+        <v>922</v>
+      </c>
+      <c r="B630" s="2">
+        <v>45703</v>
+      </c>
+      <c r="C630" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D630" s="4" t="s">
+        <v>923</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="C1:D4 E95 E99 E102 C6:D1048576">
+  <conditionalFormatting sqref="C1:D4 C6:D1048576 E95 E99 E102">
     <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>"Unplayable"</formula>
     </cfRule>
@@ -8076,7 +8099,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{923D1F1C-9339-49C8-9FCA-FF86526676FD}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A3:G54"/>
+  <dimension ref="A3:G55"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -9174,6 +9197,26 @@
       </c>
       <c r="F54" s="9">
         <v>0.4548611111111111</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A55" s="6">
+        <v>45704</v>
+      </c>
+      <c r="B55" s="10">
+        <v>0.17916666666666667</v>
+      </c>
+      <c r="C55" s="12" t="s">
+        <v>921</v>
+      </c>
+      <c r="D55" s="15" t="s">
+        <v>732</v>
+      </c>
+      <c r="E55" s="7" t="s">
+        <v>724</v>
+      </c>
+      <c r="F55" s="9">
+        <v>0.39305555555555555</v>
       </c>
     </row>
   </sheetData>

--- a/Docs/Stoned Build Change Logs.xlsx
+++ b/Docs/Stoned Build Change Logs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shield\Documents\Unity\Stonicorn\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7A3091E-529F-41F2-988E-3EE5F5F5FF05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBDE860F-07FE-487C-B59B-81A5B3B9112F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9675" yWindow="5970" windowWidth="16065" windowHeight="12330" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7920" yWindow="4215" windowWidth="17685" windowHeight="12690" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Builds" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1203" uniqueCount="924">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1211" uniqueCount="929">
   <si>
     <t>Stoned Builds Change Log</t>
   </si>
@@ -2813,6 +2813,21 @@
   </si>
   <si>
     <t>#641, #642, #634, #640</t>
+  </si>
+  <si>
+    <t>0.614</t>
+  </si>
+  <si>
+    <t>DQ: couldn't get swap upgrades, everything was too big</t>
+  </si>
+  <si>
+    <t>0_614</t>
+  </si>
+  <si>
+    <t>#642, #635, #643, #542</t>
+  </si>
+  <si>
+    <t>Remove Unity logo from splash screen, Load assets in load screen, Skin: Carrot</t>
   </si>
 </sst>
 </file>
@@ -3259,7 +3274,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:F630"/>
+  <dimension ref="A1:F631"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.42578125" style="2" bestFit="1" customWidth="1"/>
@@ -8078,9 +8093,26 @@
         <v>923</v>
       </c>
     </row>
+    <row r="631" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A631" t="s">
+        <v>926</v>
+      </c>
+      <c r="B631" s="2">
+        <v>45704</v>
+      </c>
+      <c r="C631" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D631" s="4" t="s">
+        <v>927</v>
+      </c>
+      <c r="E631" t="s">
+        <v>928</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="C1:D4 C6:D1048576 E95 E99 E102">
+  <conditionalFormatting sqref="C1:D4 E95 E99 E102 C6:D1048576">
     <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>"Unplayable"</formula>
     </cfRule>
@@ -8099,7 +8131,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{923D1F1C-9339-49C8-9FCA-FF86526676FD}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A3:G55"/>
+  <dimension ref="A3:G56"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -9217,6 +9249,29 @@
       </c>
       <c r="F55" s="9">
         <v>0.39305555555555555</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A56" s="6">
+        <v>45705</v>
+      </c>
+      <c r="B56" s="10">
+        <v>8.2638888888888887E-2</v>
+      </c>
+      <c r="C56" s="12" t="s">
+        <v>924</v>
+      </c>
+      <c r="D56" s="15" t="s">
+        <v>743</v>
+      </c>
+      <c r="E56" s="7" t="s">
+        <v>724</v>
+      </c>
+      <c r="F56" s="9">
+        <v>1.5444444444444445</v>
+      </c>
+      <c r="G56" t="s">
+        <v>925</v>
       </c>
     </row>
   </sheetData>

--- a/Docs/Stoned Build Change Logs.xlsx
+++ b/Docs/Stoned Build Change Logs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shield\Documents\Unity\Stonicorn\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBDE860F-07FE-487C-B59B-81A5B3B9112F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91FEBE01-F752-41FC-ABC9-44B42C876FD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7920" yWindow="4215" windowWidth="17685" windowHeight="12690" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13935" yWindow="5160" windowWidth="16065" windowHeight="12330" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Builds" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1211" uniqueCount="929">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1218" uniqueCount="933">
   <si>
     <t>Stoned Builds Change Log</t>
   </si>
@@ -2828,6 +2828,18 @@
   </si>
   <si>
     <t>Remove Unity logo from splash screen, Load assets in load screen, Skin: Carrot</t>
+  </si>
+  <si>
+    <t>0.615</t>
+  </si>
+  <si>
+    <t>0_615</t>
+  </si>
+  <si>
+    <t>#638, #642, #640</t>
+  </si>
+  <si>
+    <t>Fix breakable wall time rewind bugs</t>
   </si>
 </sst>
 </file>
@@ -3274,7 +3286,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:F631"/>
+  <dimension ref="A1:F632"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.42578125" style="2" bestFit="1" customWidth="1"/>
@@ -8108,6 +8120,23 @@
       </c>
       <c r="E631" t="s">
         <v>928</v>
+      </c>
+    </row>
+    <row r="632" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A632" t="s">
+        <v>930</v>
+      </c>
+      <c r="B632" s="2">
+        <v>45705</v>
+      </c>
+      <c r="C632" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D632" s="4" t="s">
+        <v>931</v>
+      </c>
+      <c r="E632" t="s">
+        <v>932</v>
       </c>
     </row>
   </sheetData>
@@ -8131,7 +8160,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{923D1F1C-9339-49C8-9FCA-FF86526676FD}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A3:G56"/>
+  <dimension ref="A3:G57"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -9272,6 +9301,26 @@
       </c>
       <c r="G56" t="s">
         <v>925</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A57" s="6">
+        <v>45706</v>
+      </c>
+      <c r="B57" s="10">
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="C57" s="12" t="s">
+        <v>929</v>
+      </c>
+      <c r="D57" s="15" t="s">
+        <v>732</v>
+      </c>
+      <c r="E57" s="7" t="s">
+        <v>724</v>
+      </c>
+      <c r="F57" s="9">
+        <v>0.37361111111111112</v>
       </c>
     </row>
   </sheetData>

--- a/Docs/Stoned Build Change Logs.xlsx
+++ b/Docs/Stoned Build Change Logs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shield\Documents\Unity\Stonicorn\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91FEBE01-F752-41FC-ABC9-44B42C876FD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96895E54-2DCC-4548-909B-2844CAD8C79C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13935" yWindow="5160" windowWidth="16065" windowHeight="12330" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="16755" yWindow="5265" windowWidth="16065" windowHeight="12330" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Builds" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1218" uniqueCount="933">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1226" uniqueCount="938">
   <si>
     <t>Stoned Builds Change Log</t>
   </si>
@@ -2840,6 +2840,21 @@
   </si>
   <si>
     <t>Fix breakable wall time rewind bugs</t>
+  </si>
+  <si>
+    <t>0.616</t>
+  </si>
+  <si>
+    <t>ran into framerate issues</t>
+  </si>
+  <si>
+    <t>0_616</t>
+  </si>
+  <si>
+    <t>#632, #645</t>
+  </si>
+  <si>
+    <t>Added mountain background to tundra</t>
   </si>
 </sst>
 </file>
@@ -3286,7 +3301,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:F632"/>
+  <dimension ref="A1:F633"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.42578125" style="2" bestFit="1" customWidth="1"/>
@@ -8137,6 +8152,23 @@
       </c>
       <c r="E632" t="s">
         <v>932</v>
+      </c>
+    </row>
+    <row r="633" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A633" t="s">
+        <v>935</v>
+      </c>
+      <c r="B633" s="2">
+        <v>45706</v>
+      </c>
+      <c r="C633" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D633" s="4" t="s">
+        <v>936</v>
+      </c>
+      <c r="E633" t="s">
+        <v>937</v>
       </c>
     </row>
   </sheetData>
@@ -8160,7 +8192,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{923D1F1C-9339-49C8-9FCA-FF86526676FD}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A3:G57"/>
+  <dimension ref="A3:G58"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -9321,6 +9353,29 @@
       </c>
       <c r="F57" s="9">
         <v>0.37361111111111112</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A58" s="6">
+        <v>45707</v>
+      </c>
+      <c r="B58" s="10">
+        <v>3.9583333333333331E-2</v>
+      </c>
+      <c r="C58" s="12" t="s">
+        <v>933</v>
+      </c>
+      <c r="D58" s="15" t="s">
+        <v>743</v>
+      </c>
+      <c r="E58" s="7" t="s">
+        <v>724</v>
+      </c>
+      <c r="F58" s="9">
+        <v>1.8486111111111112</v>
+      </c>
+      <c r="G58" t="s">
+        <v>934</v>
       </c>
     </row>
   </sheetData>

--- a/Docs/Stoned Build Change Logs.xlsx
+++ b/Docs/Stoned Build Change Logs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shield\Documents\Unity\Stonicorn\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96895E54-2DCC-4548-909B-2844CAD8C79C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{667BAF15-C378-4937-AD4E-6D39AC4521F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16755" yWindow="5265" windowWidth="16065" windowHeight="12330" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13305" yWindow="4875" windowWidth="15360" windowHeight="14535" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Builds" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1226" uniqueCount="938">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1236" uniqueCount="943">
   <si>
     <t>Stoned Builds Change Log</t>
   </si>
@@ -2855,6 +2855,21 @@
   </si>
   <si>
     <t>Added mountain background to tundra</t>
+  </si>
+  <si>
+    <t>0.525</t>
+  </si>
+  <si>
+    <t>0.617</t>
+  </si>
+  <si>
+    <t>0_617</t>
+  </si>
+  <si>
+    <t>#634, #646, #540, #530, #645</t>
+  </si>
+  <si>
+    <t>Add COGG logo, Fix bugs, Menu button mouse over</t>
   </si>
 </sst>
 </file>
@@ -3301,7 +3316,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:F633"/>
+  <dimension ref="A1:F634"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.42578125" style="2" bestFit="1" customWidth="1"/>
@@ -8169,6 +8184,23 @@
       </c>
       <c r="E633" t="s">
         <v>937</v>
+      </c>
+    </row>
+    <row r="634" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A634" t="s">
+        <v>940</v>
+      </c>
+      <c r="B634" s="2">
+        <v>45707</v>
+      </c>
+      <c r="C634" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D634" s="4" t="s">
+        <v>941</v>
+      </c>
+      <c r="E634" t="s">
+        <v>942</v>
       </c>
     </row>
   </sheetData>
@@ -8192,7 +8224,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{923D1F1C-9339-49C8-9FCA-FF86526676FD}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A3:G58"/>
+  <dimension ref="A3:G60"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -9376,6 +9408,46 @@
       </c>
       <c r="G58" t="s">
         <v>934</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A59" s="6">
+        <v>45707</v>
+      </c>
+      <c r="B59" s="10">
+        <v>0.55833333333333335</v>
+      </c>
+      <c r="C59" s="12" t="s">
+        <v>938</v>
+      </c>
+      <c r="D59" s="15" t="s">
+        <v>743</v>
+      </c>
+      <c r="E59" s="7" t="s">
+        <v>724</v>
+      </c>
+      <c r="F59" s="9">
+        <v>1.507638888888889</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A60" s="6">
+        <v>45708</v>
+      </c>
+      <c r="B60" s="10">
+        <v>0.12708333333333333</v>
+      </c>
+      <c r="C60" s="12" t="s">
+        <v>939</v>
+      </c>
+      <c r="D60" s="15" t="s">
+        <v>732</v>
+      </c>
+      <c r="E60" s="7" t="s">
+        <v>724</v>
+      </c>
+      <c r="F60" s="9">
+        <v>0.43472222222222223</v>
       </c>
     </row>
   </sheetData>

--- a/Docs/Stoned Build Change Logs.xlsx
+++ b/Docs/Stoned Build Change Logs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shield\Documents\Unity\Stonicorn\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{667BAF15-C378-4937-AD4E-6D39AC4521F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B17864A-5B9D-4FF6-8521-E65B96C2D94D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13305" yWindow="4875" windowWidth="15360" windowHeight="14535" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13950" yWindow="4530" windowWidth="16575" windowHeight="12630" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Builds" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1236" uniqueCount="943">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1240" uniqueCount="946">
   <si>
     <t>Stoned Builds Change Log</t>
   </si>
@@ -2870,6 +2870,15 @@
   </si>
   <si>
     <t>Add COGG logo, Fix bugs, Menu button mouse over</t>
+  </si>
+  <si>
+    <t>0_618</t>
+  </si>
+  <si>
+    <t>#634, #647, #648, #649</t>
+  </si>
+  <si>
+    <t>Lava shader, shifting terrain in core</t>
   </si>
 </sst>
 </file>
@@ -3316,7 +3325,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:F634"/>
+  <dimension ref="A1:F635"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.42578125" style="2" bestFit="1" customWidth="1"/>
@@ -8203,9 +8212,26 @@
         <v>942</v>
       </c>
     </row>
+    <row r="635" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A635" t="s">
+        <v>943</v>
+      </c>
+      <c r="B635" s="2">
+        <v>45712</v>
+      </c>
+      <c r="C635" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D635" s="4" t="s">
+        <v>944</v>
+      </c>
+      <c r="E635" t="s">
+        <v>945</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="C1:D4 E95 E99 E102 C6:D1048576">
+  <conditionalFormatting sqref="C1:D4 C6:D1048576 E95 E99 E102">
     <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>"Unplayable"</formula>
     </cfRule>

--- a/Docs/Stoned Build Change Logs.xlsx
+++ b/Docs/Stoned Build Change Logs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shield\Documents\Unity\Stonicorn\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B17864A-5B9D-4FF6-8521-E65B96C2D94D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C5F1D2F-6CB7-4E8E-B80E-E1558008E056}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13950" yWindow="4530" windowWidth="16575" windowHeight="12630" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20865" yWindow="2310" windowWidth="16455" windowHeight="14955" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Builds" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1240" uniqueCount="946">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1248" uniqueCount="951">
   <si>
     <t>Stoned Builds Change Log</t>
   </si>
@@ -2879,6 +2879,21 @@
   </si>
   <si>
     <t>Lava shader, shifting terrain in core</t>
+  </si>
+  <si>
+    <t>0_619</t>
+  </si>
+  <si>
+    <t>#650</t>
+  </si>
+  <si>
+    <t>Improve Moonicorn's dialogue</t>
+  </si>
+  <si>
+    <t>0.619</t>
+  </si>
+  <si>
+    <t>DQ: couldn't get 6th force launch upgrade</t>
   </si>
 </sst>
 </file>
@@ -3325,7 +3340,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:F635"/>
+  <dimension ref="A1:F636"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.42578125" style="2" bestFit="1" customWidth="1"/>
@@ -8227,6 +8242,23 @@
       </c>
       <c r="E635" t="s">
         <v>945</v>
+      </c>
+    </row>
+    <row r="636" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A636" t="s">
+        <v>946</v>
+      </c>
+      <c r="B636" s="2">
+        <v>45722</v>
+      </c>
+      <c r="C636" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D636" s="4" t="s">
+        <v>947</v>
+      </c>
+      <c r="E636" t="s">
+        <v>948</v>
       </c>
     </row>
   </sheetData>
@@ -8250,7 +8282,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{923D1F1C-9339-49C8-9FCA-FF86526676FD}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A3:G60"/>
+  <dimension ref="A3:G61"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -9474,6 +9506,29 @@
       </c>
       <c r="F60" s="9">
         <v>0.43472222222222223</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A61" s="6">
+        <v>45723</v>
+      </c>
+      <c r="B61" s="10">
+        <v>0.27638888888888891</v>
+      </c>
+      <c r="C61" s="12" t="s">
+        <v>949</v>
+      </c>
+      <c r="D61" s="15" t="s">
+        <v>743</v>
+      </c>
+      <c r="E61" s="7" t="s">
+        <v>724</v>
+      </c>
+      <c r="F61" s="9">
+        <v>1.6222222222222222</v>
+      </c>
+      <c r="G61" t="s">
+        <v>950</v>
       </c>
     </row>
   </sheetData>

--- a/Docs/Stoned Build Change Logs.xlsx
+++ b/Docs/Stoned Build Change Logs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shield\Documents\Unity\Stonicorn\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C5F1D2F-6CB7-4E8E-B80E-E1558008E056}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69ABB3A9-C307-437A-8D2E-A5EC77F38F0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20865" yWindow="2310" windowWidth="16455" windowHeight="14955" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="23805" yWindow="4095" windowWidth="16575" windowHeight="12630" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Builds" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1248" uniqueCount="951">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1252" uniqueCount="954">
   <si>
     <t>Stoned Builds Change Log</t>
   </si>
@@ -2894,6 +2894,15 @@
   </si>
   <si>
     <t>DQ: couldn't get 6th force launch upgrade</t>
+  </si>
+  <si>
+    <t>0_620</t>
+  </si>
+  <si>
+    <t>#650, #649</t>
+  </si>
+  <si>
+    <t>Improve Moonicorn's dialogue, Fix save bugs</t>
   </si>
 </sst>
 </file>
@@ -3340,7 +3349,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:F636"/>
+  <dimension ref="A1:F637"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.42578125" style="2" bestFit="1" customWidth="1"/>
@@ -8261,9 +8270,26 @@
         <v>948</v>
       </c>
     </row>
+    <row r="637" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A637" t="s">
+        <v>951</v>
+      </c>
+      <c r="B637" s="2">
+        <v>45723</v>
+      </c>
+      <c r="C637" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D637" s="4" t="s">
+        <v>952</v>
+      </c>
+      <c r="E637" t="s">
+        <v>953</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="C1:D4 C6:D1048576 E95 E99 E102">
+  <conditionalFormatting sqref="C1:D4 E95 E99 E102 C6:D1048576">
     <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>"Unplayable"</formula>
     </cfRule>

--- a/Docs/Stoned Build Change Logs.xlsx
+++ b/Docs/Stoned Build Change Logs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shield\Documents\Unity\Stonicorn\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69ABB3A9-C307-437A-8D2E-A5EC77F38F0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27D1A970-F108-4FBC-BF43-01EA6174C528}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="23805" yWindow="4095" windowWidth="16575" windowHeight="12630" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1252" uniqueCount="954">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1256" uniqueCount="957">
   <si>
     <t>Stoned Builds Change Log</t>
   </si>
@@ -2903,6 +2903,15 @@
   </si>
   <si>
     <t>Improve Moonicorn's dialogue, Fix save bugs</t>
+  </si>
+  <si>
+    <t>0_621</t>
+  </si>
+  <si>
+    <t>#649, #650</t>
+  </si>
+  <si>
+    <t>Improve dialogue, Moonicorn talks at launcher, add notices at visitor's center</t>
   </si>
 </sst>
 </file>
@@ -3349,7 +3358,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:F637"/>
+  <dimension ref="A1:F638"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.42578125" style="2" bestFit="1" customWidth="1"/>
@@ -8285,6 +8294,23 @@
       </c>
       <c r="E637" t="s">
         <v>953</v>
+      </c>
+    </row>
+    <row r="638" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A638" t="s">
+        <v>954</v>
+      </c>
+      <c r="B638" s="2">
+        <v>45724</v>
+      </c>
+      <c r="C638" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D638" s="4" t="s">
+        <v>955</v>
+      </c>
+      <c r="E638" t="s">
+        <v>956</v>
       </c>
     </row>
   </sheetData>

--- a/Docs/Stoned Build Change Logs.xlsx
+++ b/Docs/Stoned Build Change Logs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shield\Documents\Unity\Stonicorn\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27D1A970-F108-4FBC-BF43-01EA6174C528}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F606DAE-0612-496E-9CBE-4F7C93D134A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="23805" yWindow="4095" windowWidth="16575" windowHeight="12630" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19350" yWindow="4065" windowWidth="30015" windowHeight="13335" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Builds" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1256" uniqueCount="957">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1260" uniqueCount="960">
   <si>
     <t>Stoned Builds Change Log</t>
   </si>
@@ -2912,6 +2912,15 @@
   </si>
   <si>
     <t>Improve dialogue, Moonicorn talks at launcher, add notices at visitor's center</t>
+  </si>
+  <si>
+    <t>0_622</t>
+  </si>
+  <si>
+    <t>#651</t>
+  </si>
+  <si>
+    <t>Add NPC sprite: Kaki</t>
   </si>
 </sst>
 </file>
@@ -3358,7 +3367,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:F638"/>
+  <dimension ref="A1:F639"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.42578125" style="2" bestFit="1" customWidth="1"/>
@@ -8313,9 +8322,26 @@
         <v>956</v>
       </c>
     </row>
+    <row r="639" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A639" t="s">
+        <v>957</v>
+      </c>
+      <c r="B639" s="2">
+        <v>45726</v>
+      </c>
+      <c r="C639" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D639" s="4" t="s">
+        <v>958</v>
+      </c>
+      <c r="E639" t="s">
+        <v>959</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="C1:D4 E95 E99 E102 C6:D1048576">
+  <conditionalFormatting sqref="C1:D4 C6:D1048576 E95 E99 E102">
     <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>"Unplayable"</formula>
     </cfRule>

--- a/Docs/Stoned Build Change Logs.xlsx
+++ b/Docs/Stoned Build Change Logs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shield\Documents\Unity\Stonicorn\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F606DAE-0612-496E-9CBE-4F7C93D134A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FCE7181-46F6-4CFF-8830-0C23465563F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19350" yWindow="4065" windowWidth="30015" windowHeight="13335" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14190" yWindow="5370" windowWidth="22320" windowHeight="12855" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Builds" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1260" uniqueCount="960">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1266" uniqueCount="963">
   <si>
     <t>Stoned Builds Change Log</t>
   </si>
@@ -2921,6 +2921,15 @@
   </si>
   <si>
     <t>Add NPC sprite: Kaki</t>
+  </si>
+  <si>
+    <t>0.623</t>
+  </si>
+  <si>
+    <t>got an extra force launch upgrade</t>
+  </si>
+  <si>
+    <t>0_623</t>
   </si>
 </sst>
 </file>
@@ -3367,7 +3376,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:F639"/>
+  <dimension ref="A1:F640"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.42578125" style="2" bestFit="1" customWidth="1"/>
@@ -8337,6 +8346,17 @@
       </c>
       <c r="E639" t="s">
         <v>959</v>
+      </c>
+    </row>
+    <row r="640" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A640" t="s">
+        <v>962</v>
+      </c>
+      <c r="B640" s="2">
+        <v>45729</v>
+      </c>
+      <c r="C640" s="2" t="s">
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -8360,7 +8380,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{923D1F1C-9339-49C8-9FCA-FF86526676FD}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A3:G61"/>
+  <dimension ref="A3:G62"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -9607,6 +9627,29 @@
       </c>
       <c r="G61" t="s">
         <v>950</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A62" s="6">
+        <v>45730</v>
+      </c>
+      <c r="B62" s="10">
+        <v>0.14305555555555555</v>
+      </c>
+      <c r="C62" s="12" t="s">
+        <v>960</v>
+      </c>
+      <c r="D62" s="15" t="s">
+        <v>743</v>
+      </c>
+      <c r="E62" s="7" t="s">
+        <v>724</v>
+      </c>
+      <c r="F62" s="9">
+        <v>1.4277777777777778</v>
+      </c>
+      <c r="G62" t="s">
+        <v>961</v>
       </c>
     </row>
   </sheetData>

--- a/Docs/Stoned Build Change Logs.xlsx
+++ b/Docs/Stoned Build Change Logs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shield\Documents\Unity\Stonicorn\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FCE7181-46F6-4CFF-8830-0C23465563F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{460617E3-DFC3-437B-A587-095154109B74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14190" yWindow="5370" windowWidth="22320" windowHeight="12855" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="345" yWindow="5370" windowWidth="19605" windowHeight="13755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Builds" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1266" uniqueCount="963">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1269" uniqueCount="964">
   <si>
     <t>Stoned Builds Change Log</t>
   </si>
@@ -2930,6 +2930,9 @@
   </si>
   <si>
     <t>0_623</t>
+  </si>
+  <si>
+    <t>0_624</t>
   </si>
 </sst>
 </file>
@@ -3376,7 +3379,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:F640"/>
+  <dimension ref="A1:F641"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.42578125" style="2" bestFit="1" customWidth="1"/>
@@ -8357,6 +8360,20 @@
       </c>
       <c r="C640" s="2" t="s">
         <v>59</v>
+      </c>
+    </row>
+    <row r="641" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A641" t="s">
+        <v>963</v>
+      </c>
+      <c r="B641" s="2">
+        <v>45730</v>
+      </c>
+      <c r="C641" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D641" s="4" t="s">
+        <v>901</v>
       </c>
     </row>
   </sheetData>

--- a/Docs/Stoned Build Change Logs.xlsx
+++ b/Docs/Stoned Build Change Logs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shield\Documents\Unity\Stonicorn\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{460617E3-DFC3-437B-A587-095154109B74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92970873-30E9-4F10-B60F-3CD287161B08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="345" yWindow="5370" windowWidth="19605" windowHeight="13755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13695" yWindow="4200" windowWidth="20835" windowHeight="12885" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Builds" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1269" uniqueCount="964">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1273" uniqueCount="967">
   <si>
     <t>Stoned Builds Change Log</t>
   </si>
@@ -2933,6 +2933,15 @@
   </si>
   <si>
     <t>0_624</t>
+  </si>
+  <si>
+    <t>0_625</t>
+  </si>
+  <si>
+    <t>#652, #651</t>
+  </si>
+  <si>
+    <t>Add NPC sprite: Io</t>
   </si>
 </sst>
 </file>
@@ -3379,7 +3388,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:F641"/>
+  <dimension ref="A1:F642"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.42578125" style="2" bestFit="1" customWidth="1"/>
@@ -8362,7 +8371,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="641" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A641" t="s">
         <v>963</v>
       </c>
@@ -8374,6 +8383,23 @@
       </c>
       <c r="D641" s="4" t="s">
         <v>901</v>
+      </c>
+    </row>
+    <row r="642" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A642" t="s">
+        <v>964</v>
+      </c>
+      <c r="B642" s="2">
+        <v>45734</v>
+      </c>
+      <c r="C642" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D642" s="4" t="s">
+        <v>965</v>
+      </c>
+      <c r="E642" t="s">
+        <v>966</v>
       </c>
     </row>
   </sheetData>

--- a/Docs/Stoned Build Change Logs.xlsx
+++ b/Docs/Stoned Build Change Logs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shield\Documents\Unity\Stonicorn\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92970873-30E9-4F10-B60F-3CD287161B08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{609ACB6E-AEED-47F1-94DE-9EF0309D0FDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13695" yWindow="4200" windowWidth="20835" windowHeight="12885" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12825" yWindow="5085" windowWidth="21180" windowHeight="14250" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Builds" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1273" uniqueCount="967">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1277" uniqueCount="970">
   <si>
     <t>Stoned Builds Change Log</t>
   </si>
@@ -2942,6 +2942,15 @@
   </si>
   <si>
     <t>Add NPC sprite: Io</t>
+  </si>
+  <si>
+    <t>0_626</t>
+  </si>
+  <si>
+    <t>#634, #653</t>
+  </si>
+  <si>
+    <t>Add menu option: Skin</t>
   </si>
 </sst>
 </file>
@@ -3388,7 +3397,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:F642"/>
+  <dimension ref="A1:F643"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.42578125" style="2" bestFit="1" customWidth="1"/>
@@ -8400,6 +8409,23 @@
       </c>
       <c r="E642" t="s">
         <v>966</v>
+      </c>
+    </row>
+    <row r="643" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A643" t="s">
+        <v>967</v>
+      </c>
+      <c r="B643" s="2">
+        <v>45735</v>
+      </c>
+      <c r="C643" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D643" s="4" t="s">
+        <v>968</v>
+      </c>
+      <c r="E643" t="s">
+        <v>969</v>
       </c>
     </row>
   </sheetData>

--- a/Docs/Stoned Build Change Logs.xlsx
+++ b/Docs/Stoned Build Change Logs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shield\Documents\Unity\Stonicorn\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{609ACB6E-AEED-47F1-94DE-9EF0309D0FDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A141416C-8FA2-4677-95F3-229F362F6F6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12825" yWindow="5085" windowWidth="21180" windowHeight="14250" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12705" yWindow="4230" windowWidth="20835" windowHeight="12885" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Builds" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1277" uniqueCount="970">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1285" uniqueCount="975">
   <si>
     <t>Stoned Builds Change Log</t>
   </si>
@@ -2951,6 +2951,21 @@
   </si>
   <si>
     <t>Add menu option: Skin</t>
+  </si>
+  <si>
+    <t>0_627</t>
+  </si>
+  <si>
+    <t>#621, #634, #654, #542</t>
+  </si>
+  <si>
+    <t>Skin: Twilight Sparkle</t>
+  </si>
+  <si>
+    <t>0.627</t>
+  </si>
+  <si>
+    <t>DQ: crash when had all upgrades except last 2 purple upgrades, recorded time is about a minute after the crash</t>
   </si>
 </sst>
 </file>
@@ -3397,7 +3412,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:F643"/>
+  <dimension ref="A1:F644"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.42578125" style="2" bestFit="1" customWidth="1"/>
@@ -8426,6 +8441,23 @@
       </c>
       <c r="E643" t="s">
         <v>969</v>
+      </c>
+    </row>
+    <row r="644" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A644" t="s">
+        <v>970</v>
+      </c>
+      <c r="B644" s="2">
+        <v>45736</v>
+      </c>
+      <c r="C644" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D644" s="4" t="s">
+        <v>971</v>
+      </c>
+      <c r="E644" t="s">
+        <v>972</v>
       </c>
     </row>
   </sheetData>
@@ -8449,7 +8481,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{923D1F1C-9339-49C8-9FCA-FF86526676FD}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A3:G62"/>
+  <dimension ref="A3:G63"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -9719,6 +9751,29 @@
       </c>
       <c r="G62" t="s">
         <v>961</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A63" s="6">
+        <v>45737</v>
+      </c>
+      <c r="B63" s="10">
+        <v>0.17430555555555555</v>
+      </c>
+      <c r="C63" s="12" t="s">
+        <v>973</v>
+      </c>
+      <c r="D63" s="15" t="s">
+        <v>743</v>
+      </c>
+      <c r="E63" s="7" t="s">
+        <v>724</v>
+      </c>
+      <c r="F63" s="9">
+        <v>1.425</v>
+      </c>
+      <c r="G63" t="s">
+        <v>974</v>
       </c>
     </row>
   </sheetData>

--- a/Docs/Stoned Build Change Logs.xlsx
+++ b/Docs/Stoned Build Change Logs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shield\Documents\Unity\Stonicorn\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A141416C-8FA2-4677-95F3-229F362F6F6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B47ED51-C55B-4C35-9D0E-07AC7B2421B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12705" yWindow="4230" windowWidth="20835" windowHeight="12885" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9795" yWindow="6720" windowWidth="18975" windowHeight="13305" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Builds" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1285" uniqueCount="975">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1289" uniqueCount="978">
   <si>
     <t>Stoned Builds Change Log</t>
   </si>
@@ -2966,6 +2966,15 @@
   </si>
   <si>
     <t>DQ: crash when had all upgrades except last 2 purple upgrades, recorded time is about a minute after the crash</t>
+  </si>
+  <si>
+    <t>0_628</t>
+  </si>
+  <si>
+    <t>#655, #634</t>
+  </si>
+  <si>
+    <t>progress report</t>
   </si>
 </sst>
 </file>
@@ -3412,7 +3421,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:F644"/>
+  <dimension ref="A1:F645"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.42578125" style="2" bestFit="1" customWidth="1"/>
@@ -8458,6 +8467,23 @@
       </c>
       <c r="E644" t="s">
         <v>972</v>
+      </c>
+    </row>
+    <row r="645" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A645" t="s">
+        <v>975</v>
+      </c>
+      <c r="B645" s="2">
+        <v>45737</v>
+      </c>
+      <c r="C645" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D645" s="4" t="s">
+        <v>976</v>
+      </c>
+      <c r="E645" t="s">
+        <v>977</v>
       </c>
     </row>
   </sheetData>

--- a/Docs/Stoned Build Change Logs.xlsx
+++ b/Docs/Stoned Build Change Logs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shield\Documents\Unity\Stonicorn\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B47ED51-C55B-4C35-9D0E-07AC7B2421B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10403792-4FA6-44DD-AE06-9AB724637329}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9795" yWindow="6720" windowWidth="18975" windowHeight="13305" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12090" yWindow="5460" windowWidth="15330" windowHeight="10770" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Builds" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1289" uniqueCount="978">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1297" uniqueCount="982">
   <si>
     <t>Stoned Builds Change Log</t>
   </si>
@@ -2975,6 +2975,18 @@
   </si>
   <si>
     <t>progress report</t>
+  </si>
+  <si>
+    <t>0_629</t>
+  </si>
+  <si>
+    <t>0.629</t>
+  </si>
+  <si>
+    <t>DQ: crash when sun hit after getting Shelly's swap upgrade</t>
+  </si>
+  <si>
+    <t>Add NPC sprite: Kelpie, add Shelly</t>
   </si>
 </sst>
 </file>
@@ -3421,13 +3433,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:F645"/>
+  <dimension ref="A1:F646"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.42578125" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="3.85546875" style="2" customWidth="1"/>
     <col min="4" max="4" width="11.28515625" style="4" customWidth="1"/>
     <col min="5" max="5" width="24.42578125" customWidth="1"/>
+    <col min="10" max="10" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -8484,6 +8497,23 @@
       </c>
       <c r="E645" t="s">
         <v>977</v>
+      </c>
+    </row>
+    <row r="646" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A646" t="s">
+        <v>978</v>
+      </c>
+      <c r="B646" s="2">
+        <v>45739</v>
+      </c>
+      <c r="C646" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D646" s="4" t="s">
+        <v>958</v>
+      </c>
+      <c r="E646" t="s">
+        <v>981</v>
       </c>
     </row>
   </sheetData>
@@ -8507,7 +8537,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{923D1F1C-9339-49C8-9FCA-FF86526676FD}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A3:G63"/>
+  <dimension ref="A3:G64"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -9800,6 +9830,29 @@
       </c>
       <c r="G63" t="s">
         <v>974</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A64" s="6">
+        <v>45740</v>
+      </c>
+      <c r="B64" s="10">
+        <v>0.36736111111111114</v>
+      </c>
+      <c r="C64" s="12" t="s">
+        <v>979</v>
+      </c>
+      <c r="D64" s="15" t="s">
+        <v>743</v>
+      </c>
+      <c r="E64" s="7" t="s">
+        <v>724</v>
+      </c>
+      <c r="F64" s="9">
+        <v>1.2284722222222222</v>
+      </c>
+      <c r="G64" t="s">
+        <v>980</v>
       </c>
     </row>
   </sheetData>

--- a/Docs/Stoned Build Change Logs.xlsx
+++ b/Docs/Stoned Build Change Logs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shield\Documents\Unity\Stonicorn\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10403792-4FA6-44DD-AE06-9AB724637329}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{090AF12B-0FC2-4D43-B9DD-A89BDEE9E824}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12090" yWindow="5460" windowWidth="15330" windowHeight="10770" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12900" yWindow="5115" windowWidth="18450" windowHeight="13065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Builds" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1297" uniqueCount="982">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1305" uniqueCount="987">
   <si>
     <t>Stoned Builds Change Log</t>
   </si>
@@ -2987,6 +2987,21 @@
   </si>
   <si>
     <t>Add NPC sprite: Kelpie, add Shelly</t>
+  </si>
+  <si>
+    <t>0.630</t>
+  </si>
+  <si>
+    <t>DQ: stopped time briefly in moon before realizing I didn’t have 100%, DQ: could only get 92%, could only get 42/48 upgrades</t>
+  </si>
+  <si>
+    <t>0_630</t>
+  </si>
+  <si>
+    <t>#622, #646, #652, #654</t>
+  </si>
+  <si>
+    <t>Rework Flashlight ability, Refactor SavableObject to use shorts as keys instead of strings</t>
   </si>
 </sst>
 </file>
@@ -3433,7 +3448,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:F646"/>
+  <dimension ref="A1:F647"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.42578125" style="2" bestFit="1" customWidth="1"/>
@@ -8514,6 +8529,23 @@
       </c>
       <c r="E646" t="s">
         <v>981</v>
+      </c>
+    </row>
+    <row r="647" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A647" t="s">
+        <v>984</v>
+      </c>
+      <c r="B647" s="2">
+        <v>45740</v>
+      </c>
+      <c r="C647" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D647" s="4" t="s">
+        <v>985</v>
+      </c>
+      <c r="E647" t="s">
+        <v>986</v>
       </c>
     </row>
   </sheetData>
@@ -8537,7 +8569,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{923D1F1C-9339-49C8-9FCA-FF86526676FD}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A3:G64"/>
+  <dimension ref="A3:G65"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -9853,6 +9885,29 @@
       </c>
       <c r="G64" t="s">
         <v>980</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A65" s="6">
+        <v>45741</v>
+      </c>
+      <c r="B65" s="10">
+        <v>0.1875</v>
+      </c>
+      <c r="C65" s="12" t="s">
+        <v>982</v>
+      </c>
+      <c r="D65" s="15" t="s">
+        <v>743</v>
+      </c>
+      <c r="E65" s="7" t="s">
+        <v>724</v>
+      </c>
+      <c r="F65" s="9">
+        <v>1.4458333333333333</v>
+      </c>
+      <c r="G65" t="s">
+        <v>983</v>
       </c>
     </row>
   </sheetData>

--- a/Docs/Stoned Build Change Logs.xlsx
+++ b/Docs/Stoned Build Change Logs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shield\Documents\Unity\Stonicorn\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{090AF12B-0FC2-4D43-B9DD-A89BDEE9E824}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2D8A0D5-081A-4FD5-BF67-54B68952F631}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12900" yWindow="5115" windowWidth="18450" windowHeight="13065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="21045" yWindow="1710" windowWidth="15330" windowHeight="10770" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Builds" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1305" uniqueCount="987">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1309" uniqueCount="990">
   <si>
     <t>Stoned Builds Change Log</t>
   </si>
@@ -3002,6 +3002,15 @@
   </si>
   <si>
     <t>Rework Flashlight ability, Refactor SavableObject to use shorts as keys instead of strings</t>
+  </si>
+  <si>
+    <t>0_631</t>
+  </si>
+  <si>
+    <t>#655, #646, #652</t>
+  </si>
+  <si>
+    <t>Rework Flashlight ability</t>
   </si>
 </sst>
 </file>
@@ -3448,7 +3457,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:F647"/>
+  <dimension ref="A1:F648"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.42578125" style="2" bestFit="1" customWidth="1"/>
@@ -8546,6 +8555,23 @@
       </c>
       <c r="E647" t="s">
         <v>986</v>
+      </c>
+    </row>
+    <row r="648" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A648" t="s">
+        <v>987</v>
+      </c>
+      <c r="B648" s="2">
+        <v>45741</v>
+      </c>
+      <c r="C648" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D648" s="4" t="s">
+        <v>988</v>
+      </c>
+      <c r="E648" t="s">
+        <v>989</v>
       </c>
     </row>
   </sheetData>

--- a/Docs/Stoned Build Change Logs.xlsx
+++ b/Docs/Stoned Build Change Logs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shield\Documents\Unity\Stonicorn\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2D8A0D5-081A-4FD5-BF67-54B68952F631}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E1393A1-D4E6-41B5-807B-4FF9833B40DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="21045" yWindow="1710" windowWidth="15330" windowHeight="10770" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8655" yWindow="3960" windowWidth="21150" windowHeight="15015" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Builds" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1309" uniqueCount="990">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1313" uniqueCount="993">
   <si>
     <t>Stoned Builds Change Log</t>
   </si>
@@ -3011,6 +3011,15 @@
   </si>
   <si>
     <t>Rework Flashlight ability</t>
+  </si>
+  <si>
+    <t>0_632</t>
+  </si>
+  <si>
+    <t>#652, #650</t>
+  </si>
+  <si>
+    <t>Add voicelines</t>
   </si>
 </sst>
 </file>
@@ -3457,7 +3466,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:F648"/>
+  <dimension ref="A1:F649"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.42578125" style="2" bestFit="1" customWidth="1"/>
@@ -8574,9 +8583,26 @@
         <v>989</v>
       </c>
     </row>
+    <row r="649" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A649" t="s">
+        <v>990</v>
+      </c>
+      <c r="B649" s="2">
+        <v>45742</v>
+      </c>
+      <c r="C649" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D649" s="4" t="s">
+        <v>991</v>
+      </c>
+      <c r="E649" t="s">
+        <v>992</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="C1:D4 C6:D1048576 E95 E99 E102">
+  <conditionalFormatting sqref="C1:D4 E95 E99 E102 C6:D1048576">
     <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>"Unplayable"</formula>
     </cfRule>

--- a/Docs/Stoned Build Change Logs.xlsx
+++ b/Docs/Stoned Build Change Logs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shield\Documents\Unity\Stonicorn\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E1393A1-D4E6-41B5-807B-4FF9833B40DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EFAF6F0-2780-4B3F-9711-4363E76BEC82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8655" yWindow="3960" windowWidth="21150" windowHeight="15015" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="21660" yWindow="3615" windowWidth="17745" windowHeight="13995" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Builds" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1313" uniqueCount="993">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1317" uniqueCount="996">
   <si>
     <t>Stoned Builds Change Log</t>
   </si>
@@ -3020,6 +3020,15 @@
   </si>
   <si>
     <t>Add voicelines</t>
+  </si>
+  <si>
+    <t>0_633</t>
+  </si>
+  <si>
+    <t>#651, #652</t>
+  </si>
+  <si>
+    <t>Add NPC sprite: Nimbus</t>
   </si>
 </sst>
 </file>
@@ -3466,7 +3475,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:F649"/>
+  <dimension ref="A1:F650"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.42578125" style="2" bestFit="1" customWidth="1"/>
@@ -8598,6 +8607,23 @@
       </c>
       <c r="E649" t="s">
         <v>992</v>
+      </c>
+    </row>
+    <row r="650" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A650" t="s">
+        <v>993</v>
+      </c>
+      <c r="B650" s="2">
+        <v>45743</v>
+      </c>
+      <c r="C650" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D650" s="4" t="s">
+        <v>994</v>
+      </c>
+      <c r="E650" t="s">
+        <v>995</v>
       </c>
     </row>
   </sheetData>

--- a/Docs/Stoned Build Change Logs.xlsx
+++ b/Docs/Stoned Build Change Logs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shield\Documents\Unity\Stonicorn\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EFAF6F0-2780-4B3F-9711-4363E76BEC82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2925826E-286E-46D6-B358-2BC42B71D419}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="21660" yWindow="3615" windowWidth="17745" windowHeight="13995" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11505" yWindow="4830" windowWidth="17745" windowHeight="13995" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Builds" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1317" uniqueCount="996">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1321" uniqueCount="999">
   <si>
     <t>Stoned Builds Change Log</t>
   </si>
@@ -3029,6 +3029,15 @@
   </si>
   <si>
     <t>Add NPC sprite: Nimbus</t>
+  </si>
+  <si>
+    <t>0_634</t>
+  </si>
+  <si>
+    <t>#651, #652, #656</t>
+  </si>
+  <si>
+    <t>Add NPC sprite: Yellow, credits scene</t>
   </si>
 </sst>
 </file>
@@ -3475,7 +3484,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:F650"/>
+  <dimension ref="A1:F651"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.42578125" style="2" bestFit="1" customWidth="1"/>
@@ -8626,9 +8635,26 @@
         <v>995</v>
       </c>
     </row>
+    <row r="651" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A651" t="s">
+        <v>996</v>
+      </c>
+      <c r="B651" s="2">
+        <v>45744</v>
+      </c>
+      <c r="C651" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D651" s="4" t="s">
+        <v>997</v>
+      </c>
+      <c r="E651" t="s">
+        <v>998</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="C1:D4 E95 E99 E102 C6:D1048576">
+  <conditionalFormatting sqref="C1:D4 C6:D1048576 E95 E99 E102">
     <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>"Unplayable"</formula>
     </cfRule>

--- a/Docs/Stoned Build Change Logs.xlsx
+++ b/Docs/Stoned Build Change Logs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shield\Documents\Unity\Stonicorn\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2925826E-286E-46D6-B358-2BC42B71D419}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA828D9F-084C-4563-9AB1-62E441BEF05A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11505" yWindow="4830" windowWidth="17745" windowHeight="13995" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8085" yWindow="4755" windowWidth="17925" windowHeight="12225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Builds" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1321" uniqueCount="999">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1329" uniqueCount="1004">
   <si>
     <t>Stoned Builds Change Log</t>
   </si>
@@ -3038,6 +3038,21 @@
   </si>
   <si>
     <t>Add NPC sprite: Yellow, credits scene</t>
+  </si>
+  <si>
+    <t>0.635</t>
+  </si>
+  <si>
+    <t>crashed twice, several bugs showed up</t>
+  </si>
+  <si>
+    <t>0_635</t>
+  </si>
+  <si>
+    <t>#656, #646, #651</t>
+  </si>
+  <si>
+    <t>Moon moves at end, fix bugs, menu options, tutorial adjustments, flashlight upgrades, Io sprite accessories</t>
   </si>
 </sst>
 </file>
@@ -3484,7 +3499,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:F651"/>
+  <dimension ref="A1:F652"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.42578125" style="2" bestFit="1" customWidth="1"/>
@@ -8650,6 +8665,23 @@
       </c>
       <c r="E651" t="s">
         <v>998</v>
+      </c>
+    </row>
+    <row r="652" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A652" t="s">
+        <v>1001</v>
+      </c>
+      <c r="B652" s="2">
+        <v>45745</v>
+      </c>
+      <c r="C652" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D652" s="4" t="s">
+        <v>1002</v>
+      </c>
+      <c r="E652" t="s">
+        <v>1003</v>
       </c>
     </row>
   </sheetData>
@@ -8673,7 +8705,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{923D1F1C-9339-49C8-9FCA-FF86526676FD}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A3:G65"/>
+  <dimension ref="A3:G66"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -10012,6 +10044,29 @@
       </c>
       <c r="G65" t="s">
         <v>983</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A66" s="6">
+        <v>45745</v>
+      </c>
+      <c r="B66" s="10">
+        <v>0.41736111111111113</v>
+      </c>
+      <c r="C66" s="12" t="s">
+        <v>999</v>
+      </c>
+      <c r="D66" s="15" t="s">
+        <v>743</v>
+      </c>
+      <c r="E66" s="7" t="s">
+        <v>724</v>
+      </c>
+      <c r="F66" s="9">
+        <v>2.4270833333333335</v>
+      </c>
+      <c r="G66" t="s">
+        <v>1000</v>
       </c>
     </row>
   </sheetData>

--- a/Docs/Stoned Build Change Logs.xlsx
+++ b/Docs/Stoned Build Change Logs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shield\Documents\Unity\Stonicorn\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA828D9F-084C-4563-9AB1-62E441BEF05A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{962F2958-1799-49AD-8CA6-D404C5098BC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8085" yWindow="4755" windowWidth="17925" windowHeight="12225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22635" yWindow="3435" windowWidth="17745" windowHeight="13995" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Builds" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1329" uniqueCount="1004">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1334" uniqueCount="1006">
   <si>
     <t>Stoned Builds Change Log</t>
   </si>
@@ -3053,6 +3053,12 @@
   </si>
   <si>
     <t>Moon moves at end, fix bugs, menu options, tutorial adjustments, flashlight upgrades, Io sprite accessories</t>
+  </si>
+  <si>
+    <t>crashed about 4 times, was also recording it so didn't do optimal path, took small breaks to section the recording</t>
+  </si>
+  <si>
+    <t>01:37:49:00</t>
   </si>
 </sst>
 </file>
@@ -8705,13 +8711,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{923D1F1C-9339-49C8-9FCA-FF86526676FD}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A3:G66"/>
+  <dimension ref="A3:G67"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.140625" style="12"/>
     <col min="4" max="4" width="9.140625" style="15"/>
-    <col min="6" max="6" width="9.140625" style="9"/>
+    <col min="6" max="6" width="10.7109375" style="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -10067,6 +10073,29 @@
       </c>
       <c r="G66" t="s">
         <v>1000</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A67" s="6">
+        <v>45747</v>
+      </c>
+      <c r="B67" s="10">
+        <v>6.2500000000000003E-3</v>
+      </c>
+      <c r="C67" s="12" t="s">
+        <v>999</v>
+      </c>
+      <c r="D67" s="15" t="s">
+        <v>743</v>
+      </c>
+      <c r="E67" s="7" t="s">
+        <v>724</v>
+      </c>
+      <c r="F67" s="9" t="s">
+        <v>1005</v>
+      </c>
+      <c r="G67" t="s">
+        <v>1004</v>
       </c>
     </row>
   </sheetData>

--- a/Docs/Stoned Build Change Logs.xlsx
+++ b/Docs/Stoned Build Change Logs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shield\Documents\Unity\Stonicorn\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{962F2958-1799-49AD-8CA6-D404C5098BC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8F7ACE3-BC9E-4107-975F-028CC0C9836A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22635" yWindow="3435" windowWidth="17745" windowHeight="13995" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11370" yWindow="5400" windowWidth="14580" windowHeight="12315" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Builds" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1334" uniqueCount="1006">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1338" uniqueCount="1008">
   <si>
     <t>Stoned Builds Change Log</t>
   </si>
@@ -3059,6 +3059,12 @@
   </si>
   <si>
     <t>01:37:49:00</t>
+  </si>
+  <si>
+    <t>0.180</t>
+  </si>
+  <si>
+    <t>DQ: Paused time early, forgot 1 checkpoint in forest cave when time stopped</t>
   </si>
 </sst>
 </file>
@@ -8711,7 +8717,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{923D1F1C-9339-49C8-9FCA-FF86526676FD}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A3:G67"/>
+  <dimension ref="A3:G68"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -10096,6 +10102,29 @@
       </c>
       <c r="G67" t="s">
         <v>1004</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A68" s="6">
+        <v>45750</v>
+      </c>
+      <c r="B68" s="10">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="C68" s="12" t="s">
+        <v>1006</v>
+      </c>
+      <c r="D68" s="15" t="s">
+        <v>743</v>
+      </c>
+      <c r="E68" s="7" t="s">
+        <v>724</v>
+      </c>
+      <c r="F68" s="9">
+        <v>0.96111111111111114</v>
+      </c>
+      <c r="G68" t="s">
+        <v>1007</v>
       </c>
     </row>
   </sheetData>

--- a/Docs/Stoned Build Change Logs.xlsx
+++ b/Docs/Stoned Build Change Logs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shield\Documents\Unity\Stonicorn\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8F7ACE3-BC9E-4107-975F-028CC0C9836A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E8B95E3-8E10-464B-880F-7874784D5F9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11370" yWindow="5400" windowWidth="14580" windowHeight="12315" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="29745" yWindow="3600" windowWidth="15765" windowHeight="13410" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Builds" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1338" uniqueCount="1008">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1342" uniqueCount="1011">
   <si>
     <t>Stoned Builds Change Log</t>
   </si>
@@ -3065,6 +3065,15 @@
   </si>
   <si>
     <t>DQ: Paused time early, forgot 1 checkpoint in forest cave when time stopped</t>
+  </si>
+  <si>
+    <t>0_637</t>
+  </si>
+  <si>
+    <t>#660, #661</t>
+  </si>
+  <si>
+    <t>Flash Dash ability</t>
   </si>
 </sst>
 </file>
@@ -3511,7 +3520,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:F652"/>
+  <dimension ref="A1:F654"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.42578125" style="2" bestFit="1" customWidth="1"/>
@@ -8694,6 +8703,23 @@
       </c>
       <c r="E652" t="s">
         <v>1003</v>
+      </c>
+    </row>
+    <row r="654" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A654" t="s">
+        <v>1008</v>
+      </c>
+      <c r="B654" s="2">
+        <v>45799</v>
+      </c>
+      <c r="C654" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D654" s="4" t="s">
+        <v>1009</v>
+      </c>
+      <c r="E654" t="s">
+        <v>1010</v>
       </c>
     </row>
   </sheetData>

--- a/Docs/Stoned Build Change Logs.xlsx
+++ b/Docs/Stoned Build Change Logs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shield\Documents\Unity\Stonicorn\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E8B95E3-8E10-464B-880F-7874784D5F9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80CDBED8-7BFC-405B-B156-0B2E15A12C84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29745" yWindow="3600" windowWidth="15765" windowHeight="13410" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="15765" windowHeight="13410" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Builds" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1342" uniqueCount="1011">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1348" uniqueCount="1016">
   <si>
     <t>Stoned Builds Change Log</t>
   </si>
@@ -3073,7 +3073,22 @@
     <t>#660, #661</t>
   </si>
   <si>
-    <t>Flash Dash ability</t>
+    <t>0_636</t>
+  </si>
+  <si>
+    <t>Flame Dash ability</t>
+  </si>
+  <si>
+    <t>R24: change B from "2025-05-22", change E from "Flash Dash ability"</t>
+  </si>
+  <si>
+    <t>0_638</t>
+  </si>
+  <si>
+    <t>#662, #660</t>
+  </si>
+  <si>
+    <t>Battery ability</t>
   </si>
 </sst>
 </file>
@@ -3177,7 +3192,31 @@
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="6">
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF99"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDB4949"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color auto="1"/>
@@ -3520,7 +3559,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:F654"/>
+  <dimension ref="A1:F655"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.42578125" style="2" bestFit="1" customWidth="1"/>
@@ -8504,7 +8543,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="641" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A641" t="s">
         <v>963</v>
       </c>
@@ -8518,7 +8557,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="642" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A642" t="s">
         <v>964</v>
       </c>
@@ -8535,7 +8574,7 @@
         <v>966</v>
       </c>
     </row>
-    <row r="643" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A643" t="s">
         <v>967</v>
       </c>
@@ -8552,7 +8591,7 @@
         <v>969</v>
       </c>
     </row>
-    <row r="644" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A644" t="s">
         <v>970</v>
       </c>
@@ -8569,7 +8608,7 @@
         <v>972</v>
       </c>
     </row>
-    <row r="645" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A645" t="s">
         <v>975</v>
       </c>
@@ -8586,7 +8625,7 @@
         <v>977</v>
       </c>
     </row>
-    <row r="646" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A646" t="s">
         <v>978</v>
       </c>
@@ -8603,7 +8642,7 @@
         <v>981</v>
       </c>
     </row>
-    <row r="647" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A647" t="s">
         <v>984</v>
       </c>
@@ -8620,7 +8659,7 @@
         <v>986</v>
       </c>
     </row>
-    <row r="648" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A648" t="s">
         <v>987</v>
       </c>
@@ -8637,7 +8676,7 @@
         <v>989</v>
       </c>
     </row>
-    <row r="649" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A649" t="s">
         <v>990</v>
       </c>
@@ -8654,7 +8693,7 @@
         <v>992</v>
       </c>
     </row>
-    <row r="650" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A650" t="s">
         <v>993</v>
       </c>
@@ -8671,7 +8710,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="651" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A651" t="s">
         <v>996</v>
       </c>
@@ -8688,7 +8727,7 @@
         <v>998</v>
       </c>
     </row>
-    <row r="652" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A652" t="s">
         <v>1001</v>
       </c>
@@ -8705,12 +8744,17 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="654" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A653" t="s">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="654" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A654" t="s">
         <v>1008</v>
       </c>
       <c r="B654" s="2">
-        <v>45799</v>
+        <v>46164</v>
       </c>
       <c r="C654" s="2" t="s">
         <v>59</v>
@@ -8719,12 +8763,43 @@
         <v>1009</v>
       </c>
       <c r="E654" t="s">
-        <v>1010</v>
+        <v>1011</v>
+      </c>
+      <c r="F654" t="s">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="655" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A655" t="s">
+        <v>1013</v>
+      </c>
+      <c r="B655" s="2">
+        <v>46166</v>
+      </c>
+      <c r="C655" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D655" s="4" t="s">
+        <v>1014</v>
+      </c>
+      <c r="E655" t="s">
+        <v>1015</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="C1:D4 C6:D1048576 E95 E99 E102">
+  <conditionalFormatting sqref="C1:D4 E95 E99 E102">
+    <cfRule type="cellIs" dxfId="5" priority="4" operator="equal">
+      <formula>"Unplayable"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
+      <formula>"Playable"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="6" operator="equal">
+      <formula>"Funny"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C6:D1048576">
     <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>"Unplayable"</formula>
     </cfRule>
